--- a/dati.xlsx
+++ b/dati.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silvio.magurno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D734738F-CD10-4156-BD18-A5DE43B6967B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -951,7 +951,7 @@
       <sheetData sheetId="18">
         <row r="1">
           <cell r="D1">
-            <v>46189</v>
+            <v>46191</v>
           </cell>
         </row>
       </sheetData>
@@ -970,7 +970,6 @@
           <cell r="D2" t="str">
             <v>PRODUTTIVITÀ</v>
           </cell>
-          <cell r="E2"/>
           <cell r="G2" t="str">
             <v>IUQ</v>
           </cell>
@@ -980,7 +979,6 @@
           <cell r="I2" t="str">
             <v>TMG</v>
           </cell>
-          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -1013,19 +1011,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.78015480145457494</v>
+            <v>0.72754124785673957</v>
           </cell>
           <cell r="G4">
-            <v>0.65573770491803274</v>
+            <v>0.67213114754098358</v>
           </cell>
           <cell r="H4">
-            <v>2.3234936617347435E-2</v>
+            <v>2.5669146399966033E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>227.33867105656989</v>
+            <v>227.55429836428485</v>
           </cell>
         </row>
         <row r="5">
@@ -1036,19 +1034,19 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.36893801435937629</v>
+            <v>0.86290491267638891</v>
           </cell>
           <cell r="G5">
             <v>1</v>
           </cell>
           <cell r="H5">
-            <v>9.2441168513057503E-2</v>
+            <v>7.1636776366558699E-2</v>
           </cell>
           <cell r="I5">
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>257.23580959968132</v>
+            <v>261.60238883292561</v>
           </cell>
         </row>
         <row r="6">
@@ -1059,19 +1057,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.77998467430655749</v>
+            <v>0.76627854459467215</v>
           </cell>
           <cell r="G6">
-            <v>0.97257236967124849</v>
+            <v>0.97336162187647335</v>
           </cell>
           <cell r="H6">
-            <v>1.2572369671248529E-2</v>
+            <v>1.3361621876473384E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>232.52058095610263</v>
+            <v>229.06858803584402</v>
           </cell>
         </row>
         <row r="7">
@@ -1082,19 +1080,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.65147325776816389</v>
+            <v>0.6552076454190876</v>
           </cell>
           <cell r="G7">
-            <v>0.72727272727272729</v>
+            <v>0.74545454545454548</v>
           </cell>
           <cell r="H7">
-            <v>7.1194965240090752E-3</v>
+            <v>9.2251582488671775E-3</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>191.25294460641399</v>
+            <v>192.92191848460365</v>
           </cell>
         </row>
         <row r="8">
@@ -1105,19 +1103,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.70841192381313667</v>
+            <v>0.66725126033753468</v>
           </cell>
           <cell r="G8">
-            <v>0.36842105263157893</v>
+            <v>0.31578947368421051</v>
           </cell>
           <cell r="H8">
-            <v>-0.10474354147535014</v>
+            <v>-9.5194695027414414E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>133.0604838709678</v>
+            <v>131.96214308630096</v>
           </cell>
         </row>
         <row r="9">
@@ -1128,19 +1126,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.4064450352724307</v>
+            <v>0.42104095660417074</v>
           </cell>
           <cell r="G9">
-            <v>0.75</v>
+            <v>0.7142857142857143</v>
           </cell>
           <cell r="H9">
-            <v>1.3247691690088104E-4</v>
+            <v>-2.4248052802544012E-3</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>131.76258992805757</v>
+            <v>131.2671460176991</v>
           </cell>
         </row>
         <row r="10">
@@ -1151,19 +1149,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.65580302901505594</v>
+            <v>0.64395956461360626</v>
           </cell>
           <cell r="G10">
-            <v>0.40540540540540543</v>
+            <v>0.3783783783783784</v>
           </cell>
           <cell r="H10">
-            <v>-6.698668875031971E-3</v>
+            <v>-4.4968139633046692E-3</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>185.31817703399642</v>
+            <v>184.35616438356163</v>
           </cell>
         </row>
       </sheetData>
@@ -1352,33 +1350,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:D48"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="8.6640625" style="5"/>
+    <col min="6" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B2" s="50" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="51"/>
     </row>
-    <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="65" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="53"/>
       <c r="D4" s="53"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>2</v>
       </c>
@@ -1389,7 +1387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
         <v>5</v>
       </c>
@@ -1400,7 +1398,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="17" t="s">
         <v>7</v>
       </c>
@@ -1411,7 +1409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
@@ -1422,7 +1420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
         <v>11</v>
       </c>
@@ -1433,7 +1431,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>13</v>
       </c>
@@ -1445,15 +1443,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="66" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="53"/>
       <c r="D12" s="53"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>16</v>
       </c>
@@ -1464,7 +1462,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="21" t="s">
         <v>19</v>
       </c>
@@ -1473,7 +1471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="23">
         <v>0.06</v>
       </c>
@@ -1484,7 +1482,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="23">
         <v>0.04</v>
       </c>
@@ -1495,7 +1493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="23">
         <v>0.02</v>
       </c>
@@ -1506,7 +1504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="23">
         <v>0</v>
       </c>
@@ -1517,7 +1515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="24">
         <v>-1.9E-2</v>
       </c>
@@ -1528,7 +1526,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="24">
         <v>-3.9E-2</v>
       </c>
@@ -1539,7 +1537,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
         <v>20</v>
       </c>
@@ -1550,15 +1548,15 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="62" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="53"/>
       <c r="D23" s="53"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="14" t="s">
         <v>22</v>
       </c>
@@ -1569,7 +1567,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
         <v>24</v>
       </c>
@@ -1580,7 +1578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="23">
         <v>0.9</v>
       </c>
@@ -1591,7 +1589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="23">
         <v>0.85</v>
       </c>
@@ -1602,7 +1600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="25">
         <v>0.8</v>
       </c>
@@ -1613,7 +1611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="25">
         <v>0.7</v>
       </c>
@@ -1624,7 +1622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="26"/>
       <c r="C30" s="24">
         <v>0.69989999999999997</v>
@@ -1633,15 +1631,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="64" t="s">
         <v>26</v>
       </c>
       <c r="C32" s="53"/>
       <c r="D32" s="53"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="14" t="s">
         <v>27</v>
       </c>
@@ -1652,7 +1650,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
         <v>29</v>
       </c>
@@ -1661,7 +1659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="23">
         <v>8.1000000000000003E-2</v>
       </c>
@@ -1672,7 +1670,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="23">
         <v>5.0999999999999997E-2</v>
       </c>
@@ -1683,7 +1681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="25">
         <v>3.1E-2</v>
       </c>
@@ -1694,7 +1692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="25">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -1705,7 +1703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="24" t="s">
         <v>30</v>
       </c>
@@ -1716,15 +1714,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="63" t="s">
         <v>31</v>
       </c>
       <c r="C41" s="53"/>
       <c r="D41" s="53"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="14" t="s">
         <v>16</v>
       </c>
@@ -1735,7 +1733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="21" t="s">
         <v>32</v>
       </c>
@@ -1746,7 +1744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="23">
         <v>-9.9000000000000005E-2</v>
       </c>
@@ -1757,7 +1755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="23">
         <v>-4.9000000000000002E-2</v>
       </c>
@@ -1768,7 +1766,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="25">
         <v>0</v>
       </c>
@@ -1779,7 +1777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="25">
         <v>0.05</v>
       </c>
@@ -1790,7 +1788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="24">
         <v>0.1</v>
       </c>
@@ -1818,16 +1816,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:J10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="5" customWidth="1"/>
     <col min="2" max="2" width="22" style="5" customWidth="1"/>
     <col min="3" max="10" width="16" style="5" customWidth="1"/>
     <col min="11" max="11" width="2" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="5"/>
+    <col min="12" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C1" s="47" t="s">
         <v>67</v>
       </c>
@@ -1836,16 +1834,16 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C2" s="47" t="s">
         <v>68</v>
       </c>
       <c r="D2" s="48">
-        <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46189</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+        <f ca="1">'[1]Riepilogo mese per Commessa'!$D$1</f>
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>34</v>
       </c>
@@ -1874,7 +1872,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
         <v>43</v>
       </c>
@@ -1883,35 +1881,35 @@
         <v>0.64992907512514253</v>
       </c>
       <c r="D4" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.78015480145457494</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.72754124785673957</v>
       </c>
       <c r="E4" s="34">
-        <f>IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>0.13022572632943241</v>
+        <f ca="1">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <v>7.761217273159704E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65573770491803274</v>
+        <v>0.67213114754098358</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>2.3234936617347435E-2</v>
+        <v>2.5669146399966033E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
         <v>232.07216445995408</v>
       </c>
       <c r="I4" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>227.33867105656989</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>227.55429836428485</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" si="0">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-2.0396644355859361E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+        <f t="shared" ref="J4:J10" ca="1" si="0">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <v>-1.9467505317505789E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="38" t="s">
         <v>44</v>
       </c>
@@ -1920,12 +1918,12 @@
         <v>0.76087748780872522</v>
       </c>
       <c r="D5" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.36893801435937629</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.86290491267638891</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" ref="E5:E10" si="1">IF(C5=0,"",IF(D5="","",(D5-C5)))</f>
-        <v>-0.39193947344934893</v>
+        <f t="shared" ref="E5:E10" ca="1" si="1">IF(C5=0,"",IF(D5="","",(D5-C5)))</f>
+        <v>0.1020274248676637</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1933,22 +1931,22 @@
       </c>
       <c r="G5" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>9.2441168513057503E-2</v>
+        <v>7.1636776366558699E-2</v>
       </c>
       <c r="H5" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
         <v>250.86808983502152</v>
       </c>
       <c r="I5" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>257.23580959968132</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>261.60238883292561</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" si="0"/>
-        <v>2.5382741060640285E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+        <f t="shared" ca="1" si="0"/>
+        <v>4.2788618532405981E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
         <v>45</v>
       </c>
@@ -1957,35 +1955,35 @@
         <v>0.7887875467257508</v>
       </c>
       <c r="D6" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.77998467430655749</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.76627854459467215</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" si="1"/>
-        <v>-8.8028724191933083E-3</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-2.2509002131078648E-2</v>
       </c>
       <c r="F6" s="35">
-        <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97257236967124849</v>
+        <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.97336162187647335</v>
       </c>
       <c r="G6" s="36">
-        <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.2572369671248529E-2</v>
+        <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>1.3361621876473384E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>218.70039150583702</v>
       </c>
       <c r="I6" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>232.52058095610263</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>229.06858803584402</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" si="0"/>
-        <v>6.319233978095902E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+        <f t="shared" ca="1" si="0"/>
+        <v>4.7408221167863224E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
         <v>46</v>
       </c>
@@ -1994,35 +1992,35 @@
         <v>0.61747392211126917</v>
       </c>
       <c r="D7" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65147325776816389</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.6552076454190876</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" si="1"/>
-        <v>3.3999335656894725E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>3.7733723307818434E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.72727272727272729</v>
+        <v>0.74545454545454548</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>7.1194965240090752E-3</v>
+        <v>9.2251582488671775E-3</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
         <v>200.75789235670646</v>
       </c>
       <c r="I7" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>191.25294460641399</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>192.92191848460365</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" si="0"/>
-        <v>-4.734532545004054E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+        <f t="shared" ca="1" si="0"/>
+        <v>-3.9031959242627735E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="32" t="s">
         <v>47</v>
       </c>
@@ -2031,35 +2029,35 @@
         <v>0.63270000000000004</v>
       </c>
       <c r="D8" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.70841192381313667</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.66725126033753468</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" si="1"/>
-        <v>7.5711923813136628E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>3.4551260337534639E-2</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.36842105263157893</v>
+        <v>0.31578947368421051</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-0.10474354147535014</v>
+        <v>-9.5194695027414414E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>146.53039613498757</v>
       </c>
       <c r="I8" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>133.0604838709678</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>131.96214308630096</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" si="0"/>
-        <v>-9.1925720664884705E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+        <f t="shared" ca="1" si="0"/>
+        <v>-9.9421372172269054E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="38" t="s">
         <v>48</v>
       </c>
@@ -2068,35 +2066,35 @@
         <v>0.67570553852501991</v>
       </c>
       <c r="D9" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.4064450352724307</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.42104095660417074</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" si="1"/>
-        <v>-0.26926050325258921</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.25466458192084918</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.3247691690088104E-4</v>
+        <v>-2.4248052802544012E-3</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
         <v>149.81253801090318</v>
       </c>
       <c r="I9" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>131.76258992805757</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>131.2671460176991</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" si="0"/>
-        <v>-0.12048356113913485</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.12379065356902481</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="32" t="s">
         <v>49</v>
       </c>
@@ -2105,32 +2103,32 @@
         <v>0.650183652995457</v>
       </c>
       <c r="D10" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65580302901505594</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.64395956461360626</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" si="1"/>
-        <v>5.6193760195989428E-3</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-6.2240883818507342E-3</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.40540540540540543</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-6.698668875031971E-3</v>
+        <v>-4.4968139633046692E-3</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
         <v>184.92501485879896</v>
       </c>
       <c r="I10" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>185.31817703399642</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>184.35616438356163</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" si="0"/>
-        <v>2.1260626935607528E-3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-3.0761142599970955E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2142,17 +2140,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:G23"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="5" customWidth="1"/>
     <col min="2" max="2" width="22" style="5" customWidth="1"/>
     <col min="3" max="6" width="14" style="5" customWidth="1"/>
     <col min="7" max="7" width="18" style="5" customWidth="1"/>
     <col min="8" max="8" width="2" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="5"/>
+    <col min="9" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B2" s="50" t="s">
         <v>69</v>
       </c>
@@ -2162,7 +2160,7 @@
       <c r="F2" s="51"/>
       <c r="G2" s="51"/>
     </row>
-    <row r="4" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>34</v>
       </c>
@@ -2182,14 +2180,14 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="str">
         <f>'Dati Comparti'!B4</f>
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E4&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E4,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>10</v>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E4&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E4,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <v>8</v>
       </c>
       <c r="D5" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F4,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2200,22 +2198,22 @@
         <v>2</v>
       </c>
       <c r="F5" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J4&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J4,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J4&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J4,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>6</v>
       </c>
       <c r="G5" s="42">
-        <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+        <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="38" t="str">
         <f>'Dati Comparti'!B5</f>
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E5&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E5,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>-10</v>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E5&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E5,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <v>10</v>
       </c>
       <c r="D6" s="43">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F5,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2223,50 +2221,50 @@
       </c>
       <c r="E6" s="43">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!G5="","",IF('Dati Comparti'!G5&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G5,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J5&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J5,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J5&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J5,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>4</v>
       </c>
       <c r="G6" s="42">
-        <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+        <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="str">
         <f>'Dati Comparti'!B6</f>
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E6&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E6,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>-2</v>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E6&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E6,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <v>-5</v>
       </c>
       <c r="D7" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F6,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F6,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
         <v>10</v>
       </c>
       <c r="E7" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G6,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G6,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
         <v>2</v>
       </c>
       <c r="F7" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J6&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J6,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
-        <v>2</v>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J6&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J6,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <v>4</v>
       </c>
       <c r="G7" s="42">
-        <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+        <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="38" t="str">
         <f>'Dati Comparti'!B7</f>
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E7&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E7,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E7&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E7,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>4</v>
       </c>
       <c r="D8" s="43">
@@ -2278,22 +2276,22 @@
         <v>0</v>
       </c>
       <c r="F8" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J7&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J7,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J7&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J7,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>6</v>
       </c>
       <c r="G8" s="42">
-        <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
         <v>2.8</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="32" t="str">
         <f>'Dati Comparti'!B8</f>
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E8&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E8,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>8</v>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E8&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E8,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <v>4</v>
       </c>
       <c r="D9" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F8,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2304,20 +2302,20 @@
         <v>0</v>
       </c>
       <c r="F9" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J8&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J8,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J8&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J8,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>8</v>
       </c>
       <c r="G9" s="42">
-        <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+        <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="38" t="s">
         <v>48</v>
       </c>
       <c r="C10" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E9&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E9,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E9&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E9,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>-10</v>
       </c>
       <c r="D10" s="43">
@@ -2329,21 +2327,21 @@
         <v>0</v>
       </c>
       <c r="F10" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J9&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J9,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J9&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J9,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>10</v>
       </c>
       <c r="G10" s="42">
-        <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
         <v>-2.4</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="32" t="s">
         <v>49</v>
       </c>
       <c r="C11" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E10&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E10,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>2</v>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E10&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E10,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <v>-2</v>
       </c>
       <c r="D11" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F10,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2354,15 +2352,15 @@
         <v>0</v>
       </c>
       <c r="F11" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J10&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J10,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
-        <v>4</v>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J10&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J10,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <v>6</v>
       </c>
       <c r="G11" s="42">
-        <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+        <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="59" t="s">
         <v>55</v>
       </c>
@@ -2372,7 +2370,7 @@
       <c r="F13" s="53"/>
       <c r="G13" s="53"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
         <v>56</v>
       </c>
@@ -2386,119 +2384,119 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="44" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="58" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
+        <v>Editoria</v>
       </c>
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
       <c r="F15" s="53"/>
       <c r="G15" s="1">
-        <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="45" t="s">
         <v>60</v>
       </c>
       <c r="C16" s="57" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Igiene Ambientale</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
+        <v>Centro Servizi</v>
       </c>
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
       <c r="F16" s="53"/>
       <c r="G16" s="2">
-        <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="46" t="s">
         <v>61</v>
       </c>
       <c r="C17" s="54" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
-        <v>Gori</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
+        <v>Idrico</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
       <c r="F17" s="53"/>
       <c r="G17" s="3">
-        <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
         <v>2.8</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>62</v>
       </c>
       <c r="C18" s="52" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Gori</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
+        <v>Igiene Ambientale</v>
       </c>
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
       <c r="F18" s="53"/>
       <c r="G18" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>63</v>
       </c>
       <c r="C19" s="52" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
-        <v>Medicale</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
+        <v>Gori</v>
       </c>
       <c r="D19" s="53"/>
       <c r="E19" s="53"/>
       <c r="F19" s="53"/>
       <c r="G19" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C20" s="52" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
-        <v>Editoria</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
+        <v>Medicale</v>
       </c>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
       <c r="G20" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
         <v>65</v>
       </c>
       <c r="C21" s="52" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
       <c r="D21" s="53"/>
       <c r="E21" s="53"/>
       <c r="F21" s="53"/>
       <c r="G21" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
         <v>-2.4</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="55" t="s">
         <v>66</v>
       </c>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D734738F-CD10-4156-BD18-A5DE43B6967B}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DA246EC-7D8A-401E-AA63-A4573BAF7886}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -951,7 +951,7 @@
       <sheetData sheetId="18">
         <row r="1">
           <cell r="D1">
-            <v>46191</v>
+            <v>46194</v>
           </cell>
         </row>
       </sheetData>
@@ -1011,19 +1011,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.72754124785673957</v>
+            <v>0.70354524312294908</v>
           </cell>
           <cell r="G4">
-            <v>0.67213114754098358</v>
+            <v>0.70491803278688525</v>
           </cell>
           <cell r="H4">
-            <v>2.5669146399966033E-2</v>
+            <v>2.4843210488092241E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>227.55429836428485</v>
+            <v>225.58564218766094</v>
           </cell>
         </row>
         <row r="5">
@@ -1034,19 +1034,19 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.86290491267638891</v>
+            <v>0.8867965678530928</v>
           </cell>
           <cell r="G5">
             <v>1</v>
           </cell>
           <cell r="H5">
-            <v>7.1636776366558699E-2</v>
+            <v>5.9753969908182894E-2</v>
           </cell>
           <cell r="I5">
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>261.60238883292561</v>
+            <v>259.78174461501845</v>
           </cell>
         </row>
         <row r="6">
@@ -1057,19 +1057,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.76627854459467215</v>
+            <v>0.75498898293855832</v>
           </cell>
           <cell r="G6">
-            <v>0.97336162187647335</v>
+            <v>0.9730728183236188</v>
           </cell>
           <cell r="H6">
-            <v>1.3361621876473384E-2</v>
+            <v>1.307281832361884E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>229.06858803584402</v>
+            <v>229.36260862228971</v>
           </cell>
         </row>
         <row r="7">
@@ -1080,19 +1080,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.6552076454190876</v>
+            <v>0.65060845431184877</v>
           </cell>
           <cell r="G7">
             <v>0.74545454545454548</v>
           </cell>
           <cell r="H7">
-            <v>9.2251582488671775E-3</v>
+            <v>9.303454081803178E-3</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>192.92191848460365</v>
+            <v>194.51730059912961</v>
           </cell>
         </row>
         <row r="8">
@@ -1103,19 +1103,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.66725126033753468</v>
+            <v>0.65215731539940824</v>
           </cell>
           <cell r="G8">
             <v>0.31578947368421051</v>
           </cell>
           <cell r="H8">
-            <v>-9.5194695027414414E-2</v>
+            <v>-9.0978734265627886E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>131.96214308630096</v>
+            <v>131.61439954467846</v>
           </cell>
         </row>
         <row r="9">
@@ -1126,19 +1126,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.42104095660417074</v>
+            <v>0.35872686009037313</v>
           </cell>
           <cell r="G9">
             <v>0.7142857142857143</v>
           </cell>
           <cell r="H9">
-            <v>-2.4248052802544012E-3</v>
+            <v>-4.9270230592991932E-3</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>131.2671460176991</v>
+            <v>132.70302171860246</v>
           </cell>
         </row>
         <row r="10">
@@ -1149,19 +1149,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.64395956461360626</v>
+            <v>0.65012786349712914</v>
           </cell>
           <cell r="G10">
-            <v>0.3783783783783784</v>
+            <v>0.32432432432432434</v>
           </cell>
           <cell r="H10">
-            <v>-4.4968139633046692E-3</v>
+            <v>-1.2860377460777074E-2</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>184.35616438356163</v>
+            <v>187.96698316788951</v>
           </cell>
         </row>
       </sheetData>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="D2" s="48">
         <f ca="1">'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46191</v>
+        <v>46194</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" x14ac:dyDescent="0.25">
@@ -1882,19 +1882,19 @@
       </c>
       <c r="D4" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.72754124785673957</v>
+        <v>0.70354524312294908</v>
       </c>
       <c r="E4" s="34">
         <f ca="1">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>7.761217273159704E-2</v>
+        <v>5.3616167997806552E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.67213114754098358</v>
+        <v>0.70491803278688525</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>2.5669146399966033E-2</v>
+        <v>2.4843210488092241E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="I4" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>227.55429836428485</v>
+        <v>225.58564218766094</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" ca="1" si="0">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-1.9467505317505789E-2</v>
+        <v>-2.7950453633194969E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1919,11 +1919,11 @@
       </c>
       <c r="D5" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.86290491267638891</v>
+        <v>0.8867965678530928</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" ref="E5:E10" ca="1" si="1">IF(C5=0,"",IF(D5="","",(D5-C5)))</f>
-        <v>0.1020274248676637</v>
+        <v>0.12591908004436758</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G5" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>7.1636776366558699E-2</v>
+        <v>5.9753969908182894E-2</v>
       </c>
       <c r="H5" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="I5" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>261.60238883292561</v>
+        <v>259.78174461501845</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>4.2788618532405981E-2</v>
+        <v>3.5531241880379531E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -1956,19 +1956,19 @@
       </c>
       <c r="D6" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.76627854459467215</v>
+        <v>0.75498898293855832</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" ca="1" si="1"/>
-        <v>-2.2509002131078648E-2</v>
+        <v>-3.3798563787192482E-2</v>
       </c>
       <c r="F6" s="35">
         <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97336162187647335</v>
+        <v>0.9730728183236188</v>
       </c>
       <c r="G6" s="36">
         <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.3361621876473384E-2</v>
+        <v>1.307281832361884E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="I6" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>229.06858803584402</v>
+        <v>229.36260862228971</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>4.7408221167863224E-2</v>
+        <v>4.8752620162402061E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -1993,11 +1993,11 @@
       </c>
       <c r="D7" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.6552076454190876</v>
+        <v>0.65060845431184877</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" ca="1" si="1"/>
-        <v>3.7733723307818434E-2</v>
+        <v>3.3134532200579603E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>9.2251582488671775E-3</v>
+        <v>9.303454081803178E-3</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2013,11 +2013,11 @@
       </c>
       <c r="I7" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>192.92191848460365</v>
+        <v>194.51730059912961</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.9031959242627735E-2</v>
+        <v>-3.1085162751602176E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2030,11 +2030,11 @@
       </c>
       <c r="D8" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.66725126033753468</v>
+        <v>0.65215731539940824</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4551260337534639E-2</v>
+        <v>1.9457315399408204E-2</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-9.5194695027414414E-2</v>
+        <v>-9.0978734265627886E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="I8" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>131.96214308630096</v>
+        <v>131.61439954467846</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.9421372172269054E-2</v>
+        <v>-0.10179455583105164</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2067,11 +2067,11 @@
       </c>
       <c r="D9" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.42104095660417074</v>
+        <v>0.35872686009037313</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.25466458192084918</v>
+        <v>-0.31697867843464678</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>-2.4248052802544012E-3</v>
+        <v>-4.9270230592991932E-3</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2087,11 +2087,11 @@
       </c>
       <c r="I9" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>131.2671460176991</v>
+        <v>132.70302171860246</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.12379065356902481</v>
+        <v>-0.11420617072154211</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="D10" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.64395956461360626</v>
+        <v>0.65012786349712914</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" ca="1" si="1"/>
-        <v>-6.2240883818507342E-3</v>
+        <v>-5.5789498327851739E-5</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.3783783783783784</v>
+        <v>0.32432432432432434</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-4.4968139633046692E-3</v>
+        <v>-1.2860377460777074E-2</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2124,11 +2124,11 @@
       </c>
       <c r="I10" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>184.35616438356163</v>
+        <v>187.96698316788951</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.0761142599970955E-3</v>
+        <v>1.6449739433106278E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2187,11 +2187,11 @@
       </c>
       <c r="C5" s="41">
         <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E4&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E4,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F4,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!G4="","",IF('Dati Comparti'!G4&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G4,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="G5" s="42">
         <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C9" s="41">
         <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E8&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E8,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F8,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2303,11 +2303,11 @@
       </c>
       <c r="F9" s="41">
         <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J8&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J8,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G9" s="42">
         <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2353,11 +2353,11 @@
       </c>
       <c r="F11" s="41">
         <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J10&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J10,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" s="42">
         <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -2413,7 +2413,7 @@
       <c r="F16" s="53"/>
       <c r="G16" s="2">
         <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2438,14 +2438,14 @@
       </c>
       <c r="C18" s="52" t="str">
         <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Igiene Ambientale</v>
+        <v>Gori</v>
       </c>
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
       <c r="F18" s="53"/>
       <c r="G18" s="4">
         <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2477,7 +2477,7 @@
       <c r="F20" s="53"/>
       <c r="G20" s="4">
         <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DA246EC-7D8A-401E-AA63-A4573BAF7886}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0122E4B7-0C25-407D-9EC9-4B2185250864}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -951,7 +951,7 @@
       <sheetData sheetId="18">
         <row r="1">
           <cell r="D1">
-            <v>46194</v>
+            <v>46195</v>
           </cell>
         </row>
       </sheetData>
@@ -970,6 +970,7 @@
           <cell r="D2" t="str">
             <v>PRODUTTIVITÀ</v>
           </cell>
+          <cell r="E2"/>
           <cell r="G2" t="str">
             <v>IUQ</v>
           </cell>
@@ -979,6 +980,7 @@
           <cell r="I2" t="str">
             <v>TMG</v>
           </cell>
+          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -1011,7 +1013,7 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.70354524312294908</v>
+            <v>0.70126521782516538</v>
           </cell>
           <cell r="G4">
             <v>0.70491803278688525</v>
@@ -1023,7 +1025,7 @@
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>225.58564218766094</v>
+            <v>225.44881581522802</v>
           </cell>
         </row>
         <row r="5">
@@ -1034,7 +1036,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.8867965678530928</v>
+            <v>0.891002455257346</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1046,7 +1048,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>259.78174461501845</v>
+            <v>260.21003171619873</v>
           </cell>
         </row>
         <row r="6">
@@ -1057,7 +1059,7 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.75498898293855832</v>
+            <v>0.75181719486380527</v>
           </cell>
           <cell r="G6">
             <v>0.9730728183236188</v>
@@ -1080,7 +1082,7 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.65060845431184877</v>
+            <v>0.64950114461247854</v>
           </cell>
           <cell r="G7">
             <v>0.74545454545454548</v>
@@ -1092,7 +1094,7 @@
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>194.51730059912961</v>
+            <v>194.3901045701007</v>
           </cell>
         </row>
         <row r="8">
@@ -1126,7 +1128,7 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.35872686009037313</v>
+            <v>0.36700593669925491</v>
           </cell>
           <cell r="G9">
             <v>0.7142857142857143</v>
@@ -1138,7 +1140,7 @@
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>132.70302171860246</v>
+            <v>132.86390804597701</v>
           </cell>
         </row>
         <row r="10">
@@ -1149,7 +1151,7 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.65012786349712914</v>
+            <v>0.64779852443028507</v>
           </cell>
           <cell r="G10">
             <v>0.32432432432432434</v>
@@ -1161,7 +1163,7 @@
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>187.96698316788951</v>
+            <v>187.98356807511738</v>
           </cell>
         </row>
       </sheetData>
@@ -1839,8 +1841,8 @@
         <v>68</v>
       </c>
       <c r="D2" s="48">
-        <f ca="1">'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46194</v>
+        <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
+        <v>46195</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" x14ac:dyDescent="0.25">
@@ -1881,12 +1883,12 @@
         <v>0.64992907512514253</v>
       </c>
       <c r="D4" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.70354524312294908</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.70126521782516538</v>
       </c>
       <c r="E4" s="34">
-        <f ca="1">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>5.3616167997806552E-2</v>
+        <f>IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <v>5.1336142700022847E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1901,12 +1903,12 @@
         <v>232.07216445995408</v>
       </c>
       <c r="I4" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>225.58564218766094</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>225.44881581522802</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" ca="1" si="0">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-2.7950453633194969E-2</v>
+        <f t="shared" ref="J4:J10" si="0">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <v>-2.8540039087147726E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1918,12 +1920,12 @@
         <v>0.76087748780872522</v>
       </c>
       <c r="D5" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.8867965678530928</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.891002455257346</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" ref="E5:E10" ca="1" si="1">IF(C5=0,"",IF(D5="","",(D5-C5)))</f>
-        <v>0.12591908004436758</v>
+        <f t="shared" ref="E5:E10" si="1">IF(C5=0,"",IF(D5="","",(D5-C5)))</f>
+        <v>0.13012496744862079</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1938,12 +1940,12 @@
         <v>250.86808983502152</v>
       </c>
       <c r="I5" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>259.78174461501845</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>260.21003171619873</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.5531241880379531E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.7238462202668944E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -1955,19 +1957,19 @@
         <v>0.7887875467257508</v>
       </c>
       <c r="D6" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75498898293855832</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.75181719486380527</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>-3.3798563787192482E-2</v>
+        <f t="shared" si="1"/>
+        <v>-3.6970351861945527E-2</v>
       </c>
       <c r="F6" s="35">
-        <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>0.9730728183236188</v>
       </c>
       <c r="G6" s="36">
-        <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>1.307281832361884E-2</v>
       </c>
       <c r="H6" s="37">
@@ -1975,11 +1977,11 @@
         <v>218.70039150583702</v>
       </c>
       <c r="I6" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>229.36260862228971</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>4.8752620162402061E-2</v>
       </c>
     </row>
@@ -1992,12 +1994,12 @@
         <v>0.61747392211126917</v>
       </c>
       <c r="D7" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65060845431184877</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.64950114461247854</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>3.3134532200579603E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.2027222501209374E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2012,12 +2014,12 @@
         <v>200.75789235670646</v>
       </c>
       <c r="I7" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>194.51730059912961</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>194.3901045701007</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-3.1085162751602176E-2</v>
+        <f t="shared" si="0"/>
+        <v>-3.1718741972502282E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2029,11 +2031,11 @@
         <v>0.63270000000000004</v>
       </c>
       <c r="D8" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>0.65215731539940824</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>1.9457315399408204E-2</v>
       </c>
       <c r="F8" s="35">
@@ -2049,11 +2051,11 @@
         <v>146.53039613498757</v>
       </c>
       <c r="I8" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>131.61439954467846</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>-0.10179455583105164</v>
       </c>
     </row>
@@ -2066,12 +2068,12 @@
         <v>0.67570553852501991</v>
       </c>
       <c r="D9" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.35872686009037313</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.36700593669925491</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.31697867843464678</v>
+        <f t="shared" si="1"/>
+        <v>-0.308699601825765</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2086,12 +2088,12 @@
         <v>149.81253801090318</v>
       </c>
       <c r="I9" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>132.70302171860246</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>132.86390804597701</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.11420617072154211</v>
+        <f t="shared" si="0"/>
+        <v>-0.11313225308079801</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2103,12 +2105,12 @@
         <v>0.650183652995457</v>
       </c>
       <c r="D10" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65012786349712914</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.64779852443028507</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>-5.5789498327851739E-5</v>
+        <f t="shared" si="1"/>
+        <v>-2.3851285651719234E-3</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2123,12 +2125,12 @@
         <v>184.92501485879896</v>
       </c>
       <c r="I10" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>187.96698316788951</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>187.98356807511738</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>1.6449739433106278E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.6539423931661162E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2186,7 +2188,7 @@
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E4&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E4,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E4&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E4,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>6</v>
       </c>
       <c r="D5" s="41">
@@ -2198,11 +2200,11 @@
         <v>2</v>
       </c>
       <c r="F5" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J4&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J4,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J4&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J4,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>6</v>
       </c>
       <c r="G5" s="42">
-        <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
+        <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
         <v>4</v>
       </c>
     </row>
@@ -2212,7 +2214,7 @@
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E5&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E5,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E5&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E5,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>10</v>
       </c>
       <c r="D6" s="43">
@@ -2224,11 +2226,11 @@
         <v>6</v>
       </c>
       <c r="F6" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J5&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J5,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J5&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J5,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>4</v>
       </c>
       <c r="G6" s="42">
-        <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
+        <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
         <v>8.6</v>
       </c>
     </row>
@@ -2238,23 +2240,23 @@
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E6&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E6,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E6&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E6,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>-5</v>
       </c>
       <c r="D7" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F6,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F6,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
         <v>10</v>
       </c>
       <c r="E7" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G6,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G6,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
         <v>2</v>
       </c>
       <c r="F7" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J6&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J6,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J6&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J6,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>4</v>
       </c>
       <c r="G7" s="42">
-        <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
+        <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
         <v>1.8</v>
       </c>
     </row>
@@ -2264,7 +2266,7 @@
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E7&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E7,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E7&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E7,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>4</v>
       </c>
       <c r="D8" s="43">
@@ -2276,11 +2278,11 @@
         <v>0</v>
       </c>
       <c r="F8" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J7&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J7,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J7&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J7,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>6</v>
       </c>
       <c r="G8" s="42">
-        <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
+        <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
         <v>2.8</v>
       </c>
     </row>
@@ -2290,7 +2292,7 @@
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E8&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E8,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E8&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E8,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>2</v>
       </c>
       <c r="D9" s="41">
@@ -2302,11 +2304,11 @@
         <v>0</v>
       </c>
       <c r="F9" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J8&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J8,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J8&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J8,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>10</v>
       </c>
       <c r="G9" s="42">
-        <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
+        <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
         <v>1.8</v>
       </c>
     </row>
@@ -2315,7 +2317,7 @@
         <v>48</v>
       </c>
       <c r="C10" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E9&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E9,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E9&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E9,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>-10</v>
       </c>
       <c r="D10" s="43">
@@ -2327,11 +2329,11 @@
         <v>0</v>
       </c>
       <c r="F10" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J9&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J9,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J9&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J9,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>10</v>
       </c>
       <c r="G10" s="42">
-        <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
+        <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
         <v>-2.4</v>
       </c>
     </row>
@@ -2340,7 +2342,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E10&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E10,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E10&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E10,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>-2</v>
       </c>
       <c r="D11" s="41">
@@ -2352,11 +2354,11 @@
         <v>0</v>
       </c>
       <c r="F11" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J10&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J10,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f>_xlfn.SINGLE(IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J10&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J10,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>4</v>
       </c>
       <c r="G11" s="42">
-        <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
+        <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
         <v>-0.4</v>
       </c>
     </row>
@@ -2389,14 +2391,14 @@
         <v>59</v>
       </c>
       <c r="C15" s="58" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
       <c r="F15" s="53"/>
       <c r="G15" s="1">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
         <v>8.6</v>
       </c>
     </row>
@@ -2405,14 +2407,14 @@
         <v>60</v>
       </c>
       <c r="C16" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
         <v>Centro Servizi</v>
       </c>
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
       <c r="F16" s="53"/>
       <c r="G16" s="2">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
         <v>4</v>
       </c>
     </row>
@@ -2421,14 +2423,14 @@
         <v>61</v>
       </c>
       <c r="C17" s="54" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
         <v>Idrico</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
       <c r="F17" s="53"/>
       <c r="G17" s="3">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
         <v>2.8</v>
       </c>
     </row>
@@ -2437,14 +2439,14 @@
         <v>62</v>
       </c>
       <c r="C18" s="52" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
         <v>Gori</v>
       </c>
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
       <c r="F18" s="53"/>
       <c r="G18" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
         <v>1.8</v>
       </c>
     </row>
@@ -2453,14 +2455,14 @@
         <v>63</v>
       </c>
       <c r="C19" s="52" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Gori</v>
       </c>
       <c r="D19" s="53"/>
       <c r="E19" s="53"/>
       <c r="F19" s="53"/>
       <c r="G19" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
         <v>1.8</v>
       </c>
     </row>
@@ -2469,14 +2471,14 @@
         <v>64</v>
       </c>
       <c r="C20" s="52" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
         <v>Medicale</v>
       </c>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
       <c r="G20" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
         <v>-0.4</v>
       </c>
     </row>
@@ -2485,14 +2487,14 @@
         <v>65</v>
       </c>
       <c r="C21" s="52" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
       <c r="D21" s="53"/>
       <c r="E21" s="53"/>
       <c r="F21" s="53"/>
       <c r="G21" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
         <v>-2.4</v>
       </c>
     </row>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0122E4B7-0C25-407D-9EC9-4B2185250864}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97795706-EC10-4944-B3C6-A87FE0C7E6FC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -758,12 +758,27 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -787,21 +802,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -951,7 +951,7 @@
       <sheetData sheetId="18">
         <row r="1">
           <cell r="D1">
-            <v>46195</v>
+            <v>46196</v>
           </cell>
         </row>
       </sheetData>
@@ -1013,19 +1013,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.70126521782516538</v>
+            <v>0.66184355746923562</v>
           </cell>
           <cell r="G4">
-            <v>0.70491803278688525</v>
+            <v>0.75409836065573765</v>
           </cell>
           <cell r="H4">
-            <v>2.4843210488092241E-2</v>
+            <v>2.0863125544018722E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>225.44881581522802</v>
+            <v>226.35115139184316</v>
           </cell>
         </row>
         <row r="5">
@@ -1036,19 +1036,19 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.891002455257346</v>
+            <v>0.82651964577003523</v>
           </cell>
           <cell r="G5">
             <v>1</v>
           </cell>
           <cell r="H5">
-            <v>5.9753969908182894E-2</v>
+            <v>6.4507368974682039E-2</v>
           </cell>
           <cell r="I5">
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>260.21003171619873</v>
+            <v>260.99213700990953</v>
           </cell>
         </row>
         <row r="6">
@@ -1059,19 +1059,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.75181719486380527</v>
+            <v>0.74875018792618364</v>
           </cell>
           <cell r="G6">
-            <v>0.9730728183236188</v>
+            <v>0.97311105135789189</v>
           </cell>
           <cell r="H6">
-            <v>1.307281832361884E-2</v>
+            <v>1.3111051357891923E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>229.36260862228971</v>
+            <v>228.98373662811352</v>
           </cell>
         </row>
         <row r="7">
@@ -1082,19 +1082,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.64950114461247854</v>
+            <v>0.64623977878500449</v>
           </cell>
           <cell r="G7">
-            <v>0.74545454545454548</v>
+            <v>0.72727272727272729</v>
           </cell>
           <cell r="H7">
-            <v>9.303454081803178E-3</v>
+            <v>9.7777660820502731E-3</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>194.3901045701007</v>
+            <v>194.86012136581832</v>
           </cell>
         </row>
         <row r="8">
@@ -1105,19 +1105,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.65215731539940824</v>
+            <v>0.6545882222425744</v>
           </cell>
           <cell r="G8">
-            <v>0.31578947368421051</v>
+            <v>0.42105263157894735</v>
           </cell>
           <cell r="H8">
-            <v>-9.0978734265627886E-2</v>
+            <v>-8.0095997499395541E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>131.61439954467846</v>
+            <v>130.66483372610634</v>
           </cell>
         </row>
         <row r="9">
@@ -1128,19 +1128,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.36700593669925491</v>
+            <v>0.41547388291618781</v>
           </cell>
           <cell r="G9">
             <v>0.7142857142857143</v>
           </cell>
           <cell r="H9">
-            <v>-4.9270230592991932E-3</v>
+            <v>-5.0947532840328168E-3</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>132.86390804597701</v>
+            <v>133.16887966804978</v>
           </cell>
         </row>
         <row r="10">
@@ -1151,19 +1151,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.64779852443028507</v>
+            <v>0.65136882583846034</v>
           </cell>
           <cell r="G10">
-            <v>0.32432432432432434</v>
+            <v>0.27027027027027029</v>
           </cell>
           <cell r="H10">
-            <v>-1.2860377460777074E-2</v>
+            <v>-1.3478441873743046E-2</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>187.98356807511738</v>
+            <v>188.00529758011771</v>
           </cell>
         </row>
       </sheetData>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="56" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="53"/>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="57" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="53"/>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="62" t="s">
+      <c r="B23" s="52" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="53"/>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="64" t="s">
+      <c r="B32" s="55" t="s">
         <v>26</v>
       </c>
       <c r="C32" s="53"/>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="54" t="s">
         <v>31</v>
       </c>
       <c r="C41" s="53"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" x14ac:dyDescent="0.25">
@@ -1884,19 +1884,19 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.70126521782516538</v>
+        <v>0.66184355746923562</v>
       </c>
       <c r="E4" s="34">
         <f>IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>5.1336142700022847E-2</v>
+        <v>1.1914482344093091E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.70491803278688525</v>
+        <v>0.75409836065573765</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>2.4843210488092241E-2</v>
+        <v>2.0863125544018722E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1904,11 +1904,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>225.44881581522802</v>
+        <v>226.35115139184316</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="0">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-2.8540039087147726E-2</v>
+        <v>-2.4651871030823808E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1921,11 +1921,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.891002455257346</v>
+        <v>0.82651964577003523</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" ref="E5:E10" si="1">IF(C5=0,"",IF(D5="","",(D5-C5)))</f>
-        <v>0.13012496744862079</v>
+        <v>6.564215796131001E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="G5" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>5.9753969908182894E-2</v>
+        <v>6.4507368974682039E-2</v>
       </c>
       <c r="H5" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1941,11 +1941,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>260.21003171619873</v>
+        <v>260.99213700990953</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="0"/>
-        <v>3.7238462202668944E-2</v>
+        <v>4.0356057964749073E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -1958,19 +1958,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75181719486380527</v>
+        <v>0.74875018792618364</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="1"/>
-        <v>-3.6970351861945527E-2</v>
+        <v>-4.0037358799567158E-2</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.9730728183236188</v>
+        <v>0.97311105135789189</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.307281832361884E-2</v>
+        <v>1.3111051357891923E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -1978,11 +1978,11 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>229.36260862228971</v>
+        <v>228.98373662811352</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="0"/>
-        <v>4.8752620162402061E-2</v>
+        <v>4.7020241031448008E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -1995,19 +1995,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.64950114461247854</v>
+        <v>0.64623977878500449</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="1"/>
-        <v>3.2027222501209374E-2</v>
+        <v>2.8765856673735324E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.74545454545454548</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>9.303454081803178E-3</v>
+        <v>9.7777660820502731E-3</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>194.3901045701007</v>
+        <v>194.86012136581832</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="0"/>
-        <v>-3.1718741972502282E-2</v>
+        <v>-2.9377529927485956E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2032,19 +2032,19 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65215731539940824</v>
+        <v>0.6545882222425744</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="1"/>
-        <v>1.9457315399408204E-2</v>
+        <v>2.1888222242574362E-2</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.31578947368421051</v>
+        <v>0.42105263157894735</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-9.0978734265627886E-2</v>
+        <v>-8.0095997499395541E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2052,11 +2052,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>131.61439954467846</v>
+        <v>130.66483372610634</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.10179455583105164</v>
+        <v>-0.10827488922001867</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2069,11 +2069,11 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.36700593669925491</v>
+        <v>0.41547388291618781</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="1"/>
-        <v>-0.308699601825765</v>
+        <v>-0.2602316556088321</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>-4.9270230592991932E-3</v>
+        <v>-5.0947532840328168E-3</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2089,11 +2089,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>132.86390804597701</v>
+        <v>133.16887966804978</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.11313225308079801</v>
+        <v>-0.11109656483919986</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.64779852443028507</v>
+        <v>0.65136882583846034</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="1"/>
-        <v>-2.3851285651719234E-3</v>
+        <v>1.1851728430033459E-3</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.32432432432432434</v>
+        <v>0.27027027027027029</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-1.2860377460777074E-2</v>
+        <v>-1.3478441873743046E-2</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>187.98356807511738</v>
+        <v>188.00529758011771</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="0"/>
-        <v>1.6539423931661162E-2</v>
+        <v>1.6656928342932559E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="C5" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E4&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E4,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F4,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="G5" s="42">
         <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="C6" s="43">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E5&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E5,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="43">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F5,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G6" s="42">
         <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C7" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E6&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E6,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D7" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F6,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="G7" s="42">
         <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C9" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E8&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E8,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F8,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G9" s="42">
         <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C11" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E10&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E10,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D11" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F10,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2359,11 +2359,11 @@
       </c>
       <c r="G11" s="42">
         <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>-0.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="59" t="s">
+      <c r="B13" s="64" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="53"/>
@@ -2376,12 +2376,12 @@
       <c r="B14" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="65" t="s">
         <v>57</v>
       </c>
       <c r="D14" s="53"/>
       <c r="E14" s="53"/>
-      <c r="F14" s="61"/>
+      <c r="F14" s="66"/>
       <c r="G14" s="14" t="s">
         <v>58</v>
       </c>
@@ -2390,7 +2390,7 @@
       <c r="B15" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="58" t="str">
+      <c r="C15" s="63" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
@@ -2399,94 +2399,94 @@
       <c r="F15" s="53"/>
       <c r="G15" s="1">
         <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="57" t="str">
+      <c r="C16" s="62" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+        <v>Idrico</v>
       </c>
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
       <c r="F16" s="53"/>
       <c r="G16" s="2">
         <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="54" t="str">
+      <c r="C17" s="59" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
-        <v>Idrico</v>
+        <v>Igiene Ambientale</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
       <c r="F17" s="53"/>
       <c r="G17" s="3">
         <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="52" t="str">
+      <c r="C18" s="58" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Gori</v>
+        <v>Centro Servizi</v>
       </c>
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
       <c r="F18" s="53"/>
       <c r="G18" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="52" t="str">
+      <c r="C19" s="58" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
-        <v>Gori</v>
+        <v>Medicale</v>
       </c>
       <c r="D19" s="53"/>
       <c r="E19" s="53"/>
       <c r="F19" s="53"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="52" t="str">
+      <c r="C20" s="58" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
-        <v>Medicale</v>
+        <v>Gori</v>
       </c>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
       <c r="G20" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="52" t="str">
+      <c r="C21" s="58" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
@@ -2499,14 +2499,14 @@
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="55" t="s">
+      <c r="B23" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97795706-EC10-4944-B3C6-A87FE0C7E6FC}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E0B0FC6-F887-4D28-9C34-96311C21A1CD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -951,7 +951,7 @@
       <sheetData sheetId="18">
         <row r="1">
           <cell r="D1">
-            <v>46196</v>
+            <v>46197</v>
           </cell>
         </row>
       </sheetData>
@@ -970,7 +970,6 @@
           <cell r="D2" t="str">
             <v>PRODUTTIVITÀ</v>
           </cell>
-          <cell r="E2"/>
           <cell r="G2" t="str">
             <v>IUQ</v>
           </cell>
@@ -980,7 +979,6 @@
           <cell r="I2" t="str">
             <v>TMG</v>
           </cell>
-          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -1013,7 +1011,7 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.66184355746923562</v>
+            <v>0.67288126933294345</v>
           </cell>
           <cell r="G4">
             <v>0.75409836065573765</v>
@@ -1025,7 +1023,7 @@
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>226.35115139184316</v>
+            <v>226.71692117574366</v>
           </cell>
         </row>
         <row r="5">
@@ -1036,19 +1034,19 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.82651964577003523</v>
+            <v>0.84050370747214265</v>
           </cell>
           <cell r="G5">
             <v>1</v>
           </cell>
           <cell r="H5">
-            <v>6.4507368974682039E-2</v>
+            <v>4.5718168667128148E-2</v>
           </cell>
           <cell r="I5">
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>260.99213700990953</v>
+            <v>261.24873247837758</v>
           </cell>
         </row>
         <row r="6">
@@ -1059,19 +1057,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.74875018792618364</v>
+            <v>0.74406974197222586</v>
           </cell>
           <cell r="G6">
-            <v>0.97311105135789189</v>
+            <v>0.97345516269998922</v>
           </cell>
           <cell r="H6">
-            <v>1.3111051357891923E-2</v>
+            <v>1.3455162699989254E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>228.98373662811352</v>
+            <v>229.13155746827928</v>
           </cell>
         </row>
         <row r="7">
@@ -1082,7 +1080,7 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.64623977878500449</v>
+            <v>0.64454349794163956</v>
           </cell>
           <cell r="G7">
             <v>0.72727272727272729</v>
@@ -1094,7 +1092,7 @@
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>194.86012136581832</v>
+            <v>195.40958908816052</v>
           </cell>
         </row>
         <row r="8">
@@ -1105,7 +1103,7 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.6545882222425744</v>
+            <v>0.6466822714305186</v>
           </cell>
           <cell r="G8">
             <v>0.42105263157894735</v>
@@ -1117,7 +1115,7 @@
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>130.66483372610634</v>
+            <v>130.97797029702974</v>
           </cell>
         </row>
         <row r="9">
@@ -1128,7 +1126,7 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.41547388291618781</v>
+            <v>0.45692625777453644</v>
           </cell>
           <cell r="G9">
             <v>0.7142857142857143</v>
@@ -1140,7 +1138,7 @@
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>133.16887966804978</v>
+            <v>133.49923136049193</v>
           </cell>
         </row>
         <row r="10">
@@ -1151,7 +1149,7 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.65136882583846034</v>
+            <v>0.66081500499357482</v>
           </cell>
           <cell r="G10">
             <v>0.27027027027027029</v>
@@ -1163,7 +1161,7 @@
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>188.00529758011771</v>
+            <v>187.7666542265348</v>
           </cell>
         </row>
       </sheetData>
@@ -1841,7 +1839,7 @@
         <v>68</v>
       </c>
       <c r="D2" s="48">
-        <f>'[1]Riepilogo mese per Commessa'!$D$1</f>
+        <f ca="1">'[1]Riepilogo mese per Commessa'!$D$1-1</f>
         <v>46196</v>
       </c>
     </row>
@@ -1883,12 +1881,12 @@
         <v>0.64992907512514253</v>
       </c>
       <c r="D4" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.66184355746923562</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.67288126933294345</v>
       </c>
       <c r="E4" s="34">
-        <f>IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>1.1914482344093091E-2</v>
+        <f ca="1">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <v>2.2952194207800924E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1903,12 +1901,12 @@
         <v>232.07216445995408</v>
       </c>
       <c r="I4" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>226.35115139184316</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>226.71692117574366</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" si="0">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-2.4651871030823808E-2</v>
+        <f t="shared" ref="J4:J10" ca="1" si="0">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <v>-2.3075767387581318E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1920,12 +1918,12 @@
         <v>0.76087748780872522</v>
       </c>
       <c r="D5" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.82651964577003523</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.84050370747214265</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" ref="E5:E10" si="1">IF(C5=0,"",IF(D5="","",(D5-C5)))</f>
-        <v>6.564215796131001E-2</v>
+        <f t="shared" ref="E5:E10" ca="1" si="1">IF(C5=0,"",IF(D5="","",(D5-C5)))</f>
+        <v>7.962621966341743E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1933,19 +1931,19 @@
       </c>
       <c r="G5" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>6.4507368974682039E-2</v>
+        <v>4.5718168667128148E-2</v>
       </c>
       <c r="H5" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
         <v>250.86808983502152</v>
       </c>
       <c r="I5" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>260.99213700990953</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>261.24873247837758</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" si="0"/>
-        <v>4.0356057964749073E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4.1378888204484994E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -1957,32 +1955,32 @@
         <v>0.7887875467257508</v>
       </c>
       <c r="D6" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.74875018792618364</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.74406974197222586</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" si="1"/>
-        <v>-4.0037358799567158E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-4.4717804753524937E-2</v>
       </c>
       <c r="F6" s="35">
-        <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97311105135789189</v>
+        <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.97345516269998922</v>
       </c>
       <c r="G6" s="36">
-        <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.3111051357891923E-2</v>
+        <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>1.3455162699989254E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>218.70039150583702</v>
       </c>
       <c r="I6" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>228.98373662811352</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>229.13155746827928</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" si="0"/>
-        <v>4.7020241031448008E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4.7696146726668574E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -1994,12 +1992,12 @@
         <v>0.61747392211126917</v>
       </c>
       <c r="D7" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.64623977878500449</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.64454349794163956</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" si="1"/>
-        <v>2.8765856673735324E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>2.7069575830370396E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2014,12 +2012,12 @@
         <v>200.75789235670646</v>
       </c>
       <c r="I7" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>194.86012136581832</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>195.40958908816052</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" si="0"/>
-        <v>-2.9377529927485956E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-2.6640562947548217E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2031,12 +2029,12 @@
         <v>0.63270000000000004</v>
       </c>
       <c r="D8" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.6545882222425744</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.6466822714305186</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" si="1"/>
-        <v>2.1888222242574362E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1.3982271430518556E-2</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2051,12 +2049,12 @@
         <v>146.53039613498757</v>
       </c>
       <c r="I8" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>130.66483372610634</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>130.97797029702974</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" si="0"/>
-        <v>-0.10827488922001867</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.10613788161488714</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2068,12 +2066,12 @@
         <v>0.67570553852501991</v>
       </c>
       <c r="D9" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.41547388291618781</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.45692625777453644</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" si="1"/>
-        <v>-0.2602316556088321</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.21877928075048347</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2088,12 +2086,12 @@
         <v>149.81253801090318</v>
       </c>
       <c r="I9" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>133.16887966804978</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>133.49923136049193</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" si="0"/>
-        <v>-0.11109656483919986</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.10889146440616329</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2105,12 +2103,12 @@
         <v>0.650183652995457</v>
       </c>
       <c r="D10" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65136882583846034</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.66081500499357482</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" si="1"/>
-        <v>1.1851728430033459E-3</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0631351998117822E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2125,12 +2123,12 @@
         <v>184.92501485879896</v>
       </c>
       <c r="I10" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>188.00529758011771</v>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>187.7666542265348</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" si="0"/>
-        <v>1.6656928342932559E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1.5366441202698264E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2188,8 +2186,8 @@
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E4&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E4,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>2</v>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E4&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E4,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <v>4</v>
       </c>
       <c r="D5" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F4,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2200,12 +2198,12 @@
         <v>2</v>
       </c>
       <c r="F5" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J4&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J4,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J4&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J4,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>6</v>
       </c>
       <c r="G5" s="42">
-        <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>2.4</v>
+        <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2214,7 +2212,7 @@
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E5&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E5,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E5&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E5,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>8</v>
       </c>
       <c r="D6" s="43">
@@ -2223,15 +2221,15 @@
       </c>
       <c r="E6" s="43">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!G5="","",IF('Dati Comparti'!G5&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G5,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J5&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J5,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J5&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J5,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>4</v>
       </c>
       <c r="G6" s="42">
-        <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>7.8</v>
+        <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2240,23 +2238,23 @@
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E6&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E6,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E6&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E6,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>-10</v>
       </c>
       <c r="D7" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F6,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F6,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
         <v>10</v>
       </c>
       <c r="E7" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G6,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G6,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
         <v>2</v>
       </c>
       <c r="F7" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J6&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J6,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J6&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J6,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>4</v>
       </c>
       <c r="G7" s="42">
-        <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
         <v>-0.2</v>
       </c>
     </row>
@@ -2266,7 +2264,7 @@
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E7&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E7,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E7&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E7,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>4</v>
       </c>
       <c r="D8" s="43">
@@ -2278,11 +2276,11 @@
         <v>0</v>
       </c>
       <c r="F8" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J7&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J7,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J7&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J7,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>6</v>
       </c>
       <c r="G8" s="42">
-        <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
         <v>2.8</v>
       </c>
     </row>
@@ -2292,8 +2290,8 @@
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E8&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E8,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>4</v>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E8&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E8,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <v>2</v>
       </c>
       <c r="D9" s="41">
         <f>_xlfn.SINGLE(IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F8,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
@@ -2304,12 +2302,12 @@
         <v>0</v>
       </c>
       <c r="F9" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J8&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J8,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J8&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J8,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>10</v>
       </c>
       <c r="G9" s="42">
-        <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>2.6</v>
+        <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2317,7 +2315,7 @@
         <v>48</v>
       </c>
       <c r="C10" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E9&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E9,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E9&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E9,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>-10</v>
       </c>
       <c r="D10" s="43">
@@ -2329,11 +2327,11 @@
         <v>0</v>
       </c>
       <c r="F10" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J9&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J9,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J9&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J9,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>10</v>
       </c>
       <c r="G10" s="42">
-        <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
         <v>-2.4</v>
       </c>
     </row>
@@ -2342,7 +2340,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E10&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E10,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E10&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E10,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
         <v>2</v>
       </c>
       <c r="D11" s="41">
@@ -2354,11 +2352,11 @@
         <v>0</v>
       </c>
       <c r="F11" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J10&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J10,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J10&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J10,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
         <v>4</v>
       </c>
       <c r="G11" s="42">
-        <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
         <v>1.2</v>
       </c>
     </row>
@@ -2391,15 +2389,15 @@
         <v>59</v>
       </c>
       <c r="C15" s="63" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
       <c r="F15" s="53"/>
       <c r="G15" s="1">
-        <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>7.8</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
+        <v>7.4</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2407,15 +2405,15 @@
         <v>60</v>
       </c>
       <c r="C16" s="62" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Idrico</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
+        <v>Centro Servizi</v>
       </c>
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
       <c r="F16" s="53"/>
       <c r="G16" s="2">
-        <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>2.8</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2423,15 +2421,15 @@
         <v>61</v>
       </c>
       <c r="C17" s="59" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
-        <v>Igiene Ambientale</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
+        <v>Idrico</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
       <c r="F17" s="53"/>
       <c r="G17" s="3">
-        <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>2.6</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -2439,15 +2437,15 @@
         <v>62</v>
       </c>
       <c r="C18" s="58" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
+        <v>Igiene Ambientale</v>
       </c>
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
       <c r="F18" s="53"/>
       <c r="G18" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>2.4</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2455,14 +2453,14 @@
         <v>63</v>
       </c>
       <c r="C19" s="58" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Medicale</v>
       </c>
       <c r="D19" s="53"/>
       <c r="E19" s="53"/>
       <c r="F19" s="53"/>
       <c r="G19" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
         <v>1.2</v>
       </c>
     </row>
@@ -2471,14 +2469,14 @@
         <v>64</v>
       </c>
       <c r="C20" s="58" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
         <v>Gori</v>
       </c>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
       <c r="G20" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
         <v>-0.2</v>
       </c>
     </row>
@@ -2487,14 +2485,14 @@
         <v>65</v>
       </c>
       <c r="C21" s="58" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
       <c r="D21" s="53"/>
       <c r="E21" s="53"/>
       <c r="F21" s="53"/>
       <c r="G21" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
         <v>-2.4</v>
       </c>
     </row>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silvio.magurno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F7652277-F0A9-49F0-AF30-18DB2B3039C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E0B0FC6-F887-4D28-9C34-96311C21A1CD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52BA35EA-55B5-49AB-B621-9BFA023E5CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,8 @@
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,6 +41,74 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
   <si>
+    <t>🏆  SCORING COMPARTI</t>
+  </si>
+  <si>
+    <t>COMPARTO</t>
+  </si>
+  <si>
+    <t>Punteggio
+Produttività</t>
+  </si>
+  <si>
+    <t>Punteggio
+IUQ</t>
+  </si>
+  <si>
+    <t>Punteggio
+LDS</t>
+  </si>
+  <si>
+    <t>Punteggio
+TMG</t>
+  </si>
+  <si>
+    <t>SCORE
+COMPOSITO</t>
+  </si>
+  <si>
+    <t>ITS</t>
+  </si>
+  <si>
+    <t>Medicale</t>
+  </si>
+  <si>
+    <t>🥇  CLASSIFICA FINALE</t>
+  </si>
+  <si>
+    <t>Posizione</t>
+  </si>
+  <si>
+    <t>Comparto</t>
+  </si>
+  <si>
+    <t>Score Composito</t>
+  </si>
+  <si>
+    <t>🥇</t>
+  </si>
+  <si>
+    <t>🥈</t>
+  </si>
+  <si>
+    <t>🥉</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>Formula: Score = Prod×40% + IUQ×30% + LDS×20% + TMG×10%   |   Pesi e fasce modificabili nel foglio Parametri</t>
+  </si>
+  <si>
     <t>PARAMETRI DEL SISTEMA DI SCORING</t>
   </si>
   <si>
@@ -142,7 +211,10 @@
     <t>≥ +10%</t>
   </si>
   <si>
-    <t>COMPARTO</t>
+    <t>Mese</t>
+  </si>
+  <si>
+    <t>Dati al</t>
   </si>
   <si>
     <t>Produttività
@@ -190,77 +262,6 @@
   </si>
   <si>
     <t>Igiene Ambientale</t>
-  </si>
-  <si>
-    <t>ITS</t>
-  </si>
-  <si>
-    <t>Medicale</t>
-  </si>
-  <si>
-    <t>Punteggio
-Produttività</t>
-  </si>
-  <si>
-    <t>Punteggio
-IUQ</t>
-  </si>
-  <si>
-    <t>Punteggio
-LDS</t>
-  </si>
-  <si>
-    <t>Punteggio
-TMG</t>
-  </si>
-  <si>
-    <t>SCORE
-COMPOSITO</t>
-  </si>
-  <si>
-    <t>🥇  CLASSIFICA FINALE</t>
-  </si>
-  <si>
-    <t>Posizione</t>
-  </si>
-  <si>
-    <t>Comparto</t>
-  </si>
-  <si>
-    <t>Score Composito</t>
-  </si>
-  <si>
-    <t>🥇</t>
-  </si>
-  <si>
-    <t>🥈</t>
-  </si>
-  <si>
-    <t>🥉</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>Formula: Score = Prod×40% + IUQ×30% + LDS×20% + TMG×10%   |   Pesi e fasce modificabili nel foglio Parametri</t>
-  </si>
-  <si>
-    <t>Mese</t>
-  </si>
-  <si>
-    <t>Dati al</t>
-  </si>
-  <si>
-    <t>🏆  SCORING COMPARTI</t>
   </si>
 </sst>
 </file>
@@ -272,7 +273,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="mmmm\ yyyy"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,20 +384,8 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF2E5FA3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -603,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -701,19 +690,19 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="16" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -743,39 +732,19 @@
     <xf numFmtId="0" fontId="13" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -785,9 +754,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -800,8 +766,21 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -951,7 +930,7 @@
       <sheetData sheetId="18">
         <row r="1">
           <cell r="D1">
-            <v>46197</v>
+            <v>46201</v>
           </cell>
         </row>
       </sheetData>
@@ -1011,19 +990,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.67288126933294345</v>
+            <v>0.68282458488044173</v>
           </cell>
           <cell r="G4">
-            <v>0.75409836065573765</v>
+            <v>0.73770491803278693</v>
           </cell>
           <cell r="H4">
-            <v>2.0863125544018722E-2</v>
+            <v>1.8385041271582001E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>226.71692117574366</v>
+            <v>226.15563255676793</v>
           </cell>
         </row>
         <row r="5">
@@ -1034,19 +1013,19 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.84050370747214265</v>
+            <v>0.86819467121752325</v>
           </cell>
           <cell r="G5">
             <v>1</v>
           </cell>
           <cell r="H5">
-            <v>4.5718168667128148E-2</v>
+            <v>4.4226337748676597E-2</v>
           </cell>
           <cell r="I5">
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>261.24873247837758</v>
+            <v>262.48010249019137</v>
           </cell>
         </row>
         <row r="6">
@@ -1057,19 +1036,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.74406974197222586</v>
+            <v>0.74941840254753767</v>
           </cell>
           <cell r="G6">
-            <v>0.97345516269998922</v>
+            <v>0.97266627500695713</v>
           </cell>
           <cell r="H6">
-            <v>1.3455162699989254E-2</v>
+            <v>1.2666275006957162E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>229.13155746827928</v>
+            <v>229.18876561655594</v>
           </cell>
         </row>
         <row r="7">
@@ -1080,19 +1059,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.64454349794163956</v>
+            <v>0.65454664147406882</v>
           </cell>
           <cell r="G7">
-            <v>0.72727272727272729</v>
+            <v>0.69090909090909092</v>
           </cell>
           <cell r="H7">
-            <v>9.7777660820502731E-3</v>
+            <v>4.5515142288516698E-3</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>195.40958908816052</v>
+            <v>195.98527386220437</v>
           </cell>
         </row>
         <row r="8">
@@ -1103,19 +1082,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.6466822714305186</v>
+            <v>0.63406790042068617</v>
           </cell>
           <cell r="G8">
-            <v>0.42105263157894735</v>
+            <v>0.36842105263157893</v>
           </cell>
           <cell r="H8">
-            <v>-8.0095997499395541E-2</v>
+            <v>-8.1810566204557969E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>130.97797029702974</v>
+            <v>131.11163298743858</v>
           </cell>
         </row>
         <row r="9">
@@ -1126,19 +1105,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.45692625777453644</v>
+            <v>0.67236063274389102</v>
           </cell>
           <cell r="G9">
-            <v>0.7142857142857143</v>
+            <v>0.5714285714285714</v>
           </cell>
           <cell r="H9">
-            <v>-5.0947532840328168E-3</v>
+            <v>-9.0761616886004173E-3</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>133.49923136049193</v>
+            <v>135.60257214554579</v>
           </cell>
         </row>
         <row r="10">
@@ -1149,19 +1128,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.66081500499357482</v>
+            <v>0.66644558023766709</v>
           </cell>
           <cell r="G10">
-            <v>0.27027027027027029</v>
+            <v>0.21052631578947367</v>
           </cell>
           <cell r="H10">
-            <v>-1.3478441873743046E-2</v>
+            <v>-2.6689070279392116E-2</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>187.7666542265348</v>
+            <v>189.83079459798995</v>
           </cell>
         </row>
       </sheetData>
@@ -1357,114 +1336,115 @@
     <col min="3" max="3" width="18.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="8.7109375" style="5"/>
+    <col min="6" max="6" width="8.7109375" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="50" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="51"/>
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
+      <c r="B4" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6">
         <v>0.4</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="17" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C7" s="7">
         <v>0.3</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="18" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C8" s="8">
         <v>0.2</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C9" s="9">
         <v>0.1</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C10" s="10">
         <f>SUM(C6:C9)</f>
         <v>0.99999999999999989</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
+      <c r="B12" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="21" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C14" s="22"/>
       <c r="D14" s="11">
@@ -1539,7 +1519,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C21" s="24">
         <v>-0.04</v>
@@ -1550,29 +1530,29 @@
     </row>
     <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
+      <c r="B23" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="14" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D25" s="11">
         <v>10</v>
@@ -1633,26 +1613,26 @@
     </row>
     <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
+      <c r="B32" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="14" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C34" s="22"/>
       <c r="D34" s="11">
@@ -1705,7 +1685,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="24" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C39" s="24">
         <v>0.01</v>
@@ -1716,26 +1696,26 @@
     </row>
     <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
+      <c r="B41" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="14" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="21" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C43" s="23">
         <v>-0.1</v>
@@ -1793,7 +1773,7 @@
         <v>0.1</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D48" s="12">
         <v>0</v>
@@ -1822,12 +1802,13 @@
     <col min="2" max="2" width="22" style="5" customWidth="1"/>
     <col min="3" max="10" width="16" style="5" customWidth="1"/>
     <col min="11" max="11" width="2" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="8.7109375" style="5"/>
+    <col min="12" max="12" width="8.7109375" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C1" s="47" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D1" s="49">
         <f>'[1]db iniziale'!$B$1</f>
@@ -1836,45 +1817,45 @@
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C2" s="47" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D2" s="48">
         <f ca="1">'[1]Riepilogo mese per Commessa'!$D$1-1</f>
-        <v>46196</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="I3" s="31" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C4" s="33">
         <f>INDEX([1]dati_comparti!D:D,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1882,19 +1863,19 @@
       </c>
       <c r="D4" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.67288126933294345</v>
+        <v>0.68282458488044173</v>
       </c>
       <c r="E4" s="34">
-        <f ca="1">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>2.2952194207800924E-2</v>
+        <f t="shared" ref="E4:E10" ca="1" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <v>3.2895509755299202E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.75409836065573765</v>
+        <v>0.73770491803278693</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>2.0863125544018722E-2</v>
+        <v>1.8385041271582001E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1902,16 +1883,16 @@
       </c>
       <c r="I4" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>226.71692117574366</v>
+        <v>226.15563255676793</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" ca="1" si="0">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-2.3075767387581318E-2</v>
+        <f t="shared" ref="J4:J10" ca="1" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <v>-2.5494362570169848E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="38" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C5" s="33">
         <f>INDEX([1]dati_comparti!D:D,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1919,11 +1900,11 @@
       </c>
       <c r="D5" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.84050370747214265</v>
+        <v>0.86819467121752325</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" ref="E5:E10" ca="1" si="1">IF(C5=0,"",IF(D5="","",(D5-C5)))</f>
-        <v>7.962621966341743E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0.10731718340879803</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1931,7 +1912,7 @@
       </c>
       <c r="G5" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.5718168667128148E-2</v>
+        <v>4.4226337748676597E-2</v>
       </c>
       <c r="H5" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1939,16 +1920,16 @@
       </c>
       <c r="I5" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>261.24873247837758</v>
+        <v>262.48010249019137</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.1378888204484994E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>4.6287324397480213E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C6" s="33">
         <f>INDEX([1]dati_comparti!D:D,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -1956,19 +1937,19 @@
       </c>
       <c r="D6" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.74406974197222586</v>
+        <v>0.74941840254753767</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>-4.4717804753524937E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-3.9369144178213134E-2</v>
       </c>
       <c r="F6" s="35">
         <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97345516269998922</v>
+        <v>0.97266627500695713</v>
       </c>
       <c r="G6" s="36">
         <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.3455162699989254E-2</v>
+        <v>1.2666275006957162E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -1976,16 +1957,16 @@
       </c>
       <c r="I6" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>229.13155746827928</v>
+        <v>229.18876561655594</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.7696146726668574E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>4.7957729012291193E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C7" s="33">
         <f>INDEX([1]dati_comparti!D:D,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -1993,19 +1974,19 @@
       </c>
       <c r="D7" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.64454349794163956</v>
+        <v>0.65454664147406882</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.7069575830370396E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>3.7072719362799655E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.72727272727272729</v>
+        <v>0.69090909090909092</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>9.7777660820502731E-3</v>
+        <v>4.5515142288516698E-3</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2013,16 +1994,16 @@
       </c>
       <c r="I7" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>195.40958908816052</v>
+        <v>195.98527386220437</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-2.6640562947548217E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-2.3773005576399022E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="32" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C8" s="33">
         <f>INDEX([1]dati_comparti!D:D,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2030,19 +2011,19 @@
       </c>
       <c r="D8" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.6466822714305186</v>
+        <v>0.63406790042068617</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.3982271430518556E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1.36790042068613E-3</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.42105263157894735</v>
+        <v>0.36842105263157893</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-8.0095997499395541E-2</v>
+        <v>-8.1810566204557969E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2050,16 +2031,16 @@
       </c>
       <c r="I8" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>130.97797029702974</v>
+        <v>131.11163298743858</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.10613788161488714</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.10522569756342449</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="38" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="C9" s="33">
         <f>INDEX([1]dati_comparti!D:D,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2067,19 +2048,19 @@
       </c>
       <c r="D9" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.45692625777453644</v>
+        <v>0.67236063274389102</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.21877928075048347</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-3.3449057811288929E-3</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>-5.0947532840328168E-3</v>
+        <v>-9.0761616886004173E-3</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2087,16 +2068,16 @@
       </c>
       <c r="I9" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>133.49923136049193</v>
+        <v>135.60257214554579</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.10889146440616329</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-9.4851646290934635E-2</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="32" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="C10" s="33">
         <f>INDEX([1]dati_comparti!D:D,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2104,19 +2085,19 @@
       </c>
       <c r="D10" s="33">
         <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.66081500499357482</v>
+        <v>0.66644558023766709</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.0631351998117822E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1.6261927242210095E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.27027027027027029</v>
+        <v>0.21052631578947367</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-1.3478441873743046E-2</v>
+        <v>-2.6689070279392116E-2</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2124,11 +2105,11 @@
       </c>
       <c r="I10" s="37">
         <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>187.7666542265348</v>
+        <v>189.83079459798995</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>1.5366441202698264E-2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>2.6528480978827224E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2147,12 +2128,13 @@
     <col min="3" max="6" width="14" style="5" customWidth="1"/>
     <col min="7" max="7" width="18" style="5" customWidth="1"/>
     <col min="8" max="8" width="2" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="8.7109375" style="5"/>
+    <col min="9" max="9" width="8.7109375" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="50" t="s">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="51"/>
@@ -2160,24 +2142,24 @@
       <c r="F2" s="51"/>
       <c r="G2" s="51"/>
     </row>
-    <row r="4" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -2186,19 +2168,19 @@
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E4&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E4,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>4</v>
       </c>
       <c r="D5" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F4,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
+        <f>IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F4&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F4&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F4&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F4&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>2</v>
       </c>
       <c r="E5" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!G4="","",IF('Dati Comparti'!G4&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G4,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
+        <f>IF('Dati Comparti'!G4="","",IF('Dati Comparti'!G4&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G4&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G4&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G4&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G4&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>2</v>
       </c>
       <c r="F5" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J4&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J4,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G5" s="42">
@@ -2212,24 +2194,24 @@
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E5&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E5,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>8</v>
+        <f ca="1">IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>10</v>
       </c>
       <c r="D6" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F5,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
+        <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>10</v>
       </c>
       <c r="E6" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!G5="","",IF('Dati Comparti'!G5&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G5,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
+        <f>IF('Dati Comparti'!G5="","",IF('Dati Comparti'!G5&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G5&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G5&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G5&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G5&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>4</v>
       </c>
       <c r="F6" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J5&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J5,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G6" s="42">
         <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>7.4</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2238,24 +2220,24 @@
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E6&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E6,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>-10</v>
+        <f ca="1">IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-5</v>
       </c>
       <c r="D7" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F6,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
+        <f ca="1">IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>10</v>
       </c>
       <c r="E7" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G6,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
+        <f ca="1">IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>2</v>
       </c>
       <c r="F7" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J6&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J6,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G7" s="42">
         <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>-0.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2264,24 +2246,24 @@
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E7&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E7,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>4</v>
       </c>
       <c r="D8" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F7,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
-        <v>2</v>
+        <f>IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F7&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F7&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F7&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F7&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
+        <v>0</v>
       </c>
       <c r="E8" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!G7="","",IF('Dati Comparti'!G7&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G7,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
+        <f>IF('Dati Comparti'!G7="","",IF('Dati Comparti'!G7&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G7&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G7&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G7&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G7&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>0</v>
       </c>
       <c r="F8" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J7&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J7,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G8" s="42">
         <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>2.8</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2290,19 +2272,19 @@
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E8&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E8,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>2</v>
       </c>
       <c r="D9" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F8,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
+        <f>IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F8&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F8&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F8&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F8&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>0</v>
       </c>
       <c r="E9" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!G8="","",IF('Dati Comparti'!G8&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G8,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
+        <f>IF('Dati Comparti'!G8="","",IF('Dati Comparti'!G8&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G8&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G8&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G8&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G8&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>0</v>
       </c>
       <c r="F9" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J8&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J8,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>10</v>
       </c>
       <c r="G9" s="42">
@@ -2312,47 +2294,47 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="38" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="C10" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E9&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E9,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
-        <v>-10</v>
+        <f ca="1">IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-2</v>
       </c>
       <c r="D10" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!F9="","",IF('Dati Comparti'!F9&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F9,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
-        <v>2</v>
+        <f>IF('Dati Comparti'!F9="","",IF('Dati Comparti'!F9&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F9&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F9&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F9&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F9&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
+        <v>0</v>
       </c>
       <c r="E10" s="43">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!G9="","",IF('Dati Comparti'!G9&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G9,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
+        <f>IF('Dati Comparti'!G9="","",IF('Dati Comparti'!G9&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G9&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G9&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G9&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G9&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>0</v>
       </c>
       <c r="F10" s="43">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J9&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J9,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
-        <v>10</v>
+        <f ca="1">IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>8</v>
       </c>
       <c r="G10" s="42">
         <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
-        <v>-2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="32" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="C11" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!D14,IF('Dati Comparti'!E10&lt;-0.04,Parametri!D21,_xlfn.XLOOKUP('Dati Comparti'!E10,Parametri!B15:B20,Parametri!D15:D20,,-1,1)))))</f>
+        <f ca="1">IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>2</v>
       </c>
       <c r="D11" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!D25,_xlfn.XLOOKUP('Dati Comparti'!F10,Parametri!B26:B30,Parametri!D26:D30,Parametri!D30,-1,1))))</f>
+        <f>IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F10&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F10&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F10&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F10&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>0</v>
       </c>
       <c r="E11" s="41">
-        <f>_xlfn.SINGLE(IF('Dati Comparti'!G10="","",IF('Dati Comparti'!G10&gt;0.12,Parametri!D34,_xlfn.XLOOKUP('Dati Comparti'!G10,Parametri!C35:C39,Parametri!D35:D39,Parametri!D39,1,1))))</f>
+        <f>IF('Dati Comparti'!G10="","",IF('Dati Comparti'!G10&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G10&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G10&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G10&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G10&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>0</v>
       </c>
       <c r="F11" s="41">
-        <f ca="1">_xlfn.SINGLE(IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=-0.1,Parametri!D43,IF('Dati Comparti'!J10&gt;=0.1,Parametri!D48,_xlfn.XLOOKUP('Dati Comparti'!J10,Parametri!C44:C47,Parametri!D44:D47,,1,1)))))</f>
+        <f ca="1">IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G11" s="42">
@@ -2361,56 +2343,56 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
+      <c r="B13" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="65" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="66"/>
+        <v>10</v>
+      </c>
+      <c r="C14" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="59"/>
       <c r="G14" s="14" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="63" t="str">
+        <v>13</v>
+      </c>
+      <c r="C15" s="56" t="str">
         <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
       <c r="G15" s="1">
         <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>7.4</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="62" t="str">
+        <v>14</v>
+      </c>
+      <c r="C16" s="55" t="str">
         <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
         <v>Centro Servizi</v>
       </c>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
       <c r="G16" s="2">
         <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
         <v>3.2</v>
@@ -2418,31 +2400,31 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="59" t="str">
+        <v>15</v>
+      </c>
+      <c r="C17" s="53" t="str">
         <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
         <v>Idrico</v>
       </c>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
       <c r="G17" s="3">
         <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>2.8</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="58" t="str">
+        <v>16</v>
+      </c>
+      <c r="C18" s="52" t="str">
         <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Igiene Ambientale</v>
-      </c>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
+        <v>Gori</v>
+      </c>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
       <c r="G18" s="4">
         <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
         <v>1.8</v>
@@ -2450,61 +2432,61 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="58" t="str">
+        <v>17</v>
+      </c>
+      <c r="C19" s="52" t="str">
         <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
-        <v>Medicale</v>
-      </c>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
+        <v>Gori</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
       <c r="G19" s="4">
         <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="58" t="str">
+        <v>18</v>
+      </c>
+      <c r="C20" s="52" t="str">
         <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
-        <v>Gori</v>
-      </c>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
+        <v>Medicale</v>
+      </c>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
       <c r="G20" s="4">
         <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="58" t="str">
+        <v>19</v>
+      </c>
+      <c r="C21" s="52" t="str">
         <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
       <c r="G21" s="4">
         <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
-        <v>-2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="60" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
+      <c r="B23" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silvio.magurno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52BA35EA-55B5-49AB-B621-9BFA023E5CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{52BA35EA-55B5-49AB-B621-9BFA023E5CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3855C0BE-F9D4-46D9-A8DF-CF5FFB2AE146}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -930,7 +929,7 @@
       <sheetData sheetId="18">
         <row r="1">
           <cell r="D1">
-            <v>46201</v>
+            <v>46203</v>
           </cell>
         </row>
       </sheetData>
@@ -949,6 +948,7 @@
           <cell r="D2" t="str">
             <v>PRODUTTIVITÀ</v>
           </cell>
+          <cell r="E2"/>
           <cell r="G2" t="str">
             <v>IUQ</v>
           </cell>
@@ -958,6 +958,7 @@
           <cell r="I2" t="str">
             <v>TMG</v>
           </cell>
+          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -990,19 +991,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.68282458488044173</v>
+            <v>0.74009444397480006</v>
           </cell>
           <cell r="G4">
-            <v>0.73770491803278693</v>
+            <v>0.70491803278688525</v>
           </cell>
           <cell r="H4">
-            <v>1.8385041271582001E-2</v>
+            <v>1.6446205494982522E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>226.15563255676793</v>
+            <v>225.68464703193365</v>
           </cell>
         </row>
         <row r="5">
@@ -1013,19 +1014,19 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.86819467121752325</v>
+            <v>0.72184902227872527</v>
           </cell>
           <cell r="G5">
             <v>1</v>
           </cell>
           <cell r="H5">
-            <v>4.4226337748676597E-2</v>
+            <v>3.4107620812836123E-2</v>
           </cell>
           <cell r="I5">
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>262.48010249019137</v>
+            <v>261.89621866009043</v>
           </cell>
         </row>
         <row r="6">
@@ -1036,19 +1037,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.74941840254753767</v>
+            <v>0.73183157444710967</v>
           </cell>
           <cell r="G6">
-            <v>0.97266627500695713</v>
+            <v>0.97327656236869375</v>
           </cell>
           <cell r="H6">
-            <v>1.2666275006957162E-2</v>
+            <v>1.3276562368693789E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>229.18876561655594</v>
+            <v>229.00233127068643</v>
           </cell>
         </row>
         <row r="7">
@@ -1059,19 +1060,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.65454664147406882</v>
+            <v>0.65658489452686997</v>
           </cell>
           <cell r="G7">
             <v>0.69090909090909092</v>
           </cell>
           <cell r="H7">
-            <v>4.5515142288516698E-3</v>
+            <v>6.3545518819056353E-3</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>195.98527386220437</v>
+            <v>196.24635372788543</v>
           </cell>
         </row>
         <row r="8">
@@ -1082,19 +1083,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.63406790042068617</v>
+            <v>0.59405152850266629</v>
           </cell>
           <cell r="G8">
             <v>0.36842105263157893</v>
           </cell>
           <cell r="H8">
-            <v>-8.1810566204557969E-2</v>
+            <v>-7.9910258209150944E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>131.11163298743858</v>
+            <v>132.64600764383846</v>
           </cell>
         </row>
         <row r="9">
@@ -1105,19 +1106,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.67236063274389102</v>
+            <v>0.59814440235062616</v>
           </cell>
           <cell r="G9">
             <v>0.5714285714285714</v>
           </cell>
           <cell r="H9">
-            <v>-9.0761616886004173E-3</v>
+            <v>-8.8618206206812957E-3</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>135.60257214554579</v>
+            <v>134.5204081632653</v>
           </cell>
         </row>
         <row r="10">
@@ -1128,19 +1129,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.66644558023766709</v>
+            <v>0.67352781498591241</v>
           </cell>
           <cell r="G10">
             <v>0.21052631578947367</v>
           </cell>
           <cell r="H10">
-            <v>-2.6689070279392116E-2</v>
+            <v>-2.9470943955545014E-2</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>189.83079459798995</v>
+            <v>189.35652052042698</v>
           </cell>
         </row>
       </sheetData>
@@ -1820,8 +1821,8 @@
         <v>56</v>
       </c>
       <c r="D2" s="48">
-        <f ca="1">'[1]Riepilogo mese per Commessa'!$D$1-1</f>
-        <v>46200</v>
+        <f>'[1]Riepilogo mese per Commessa'!$D$1-1</f>
+        <v>46202</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1862,32 +1863,32 @@
         <v>0.64992907512514253</v>
       </c>
       <c r="D4" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.68282458488044173</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.74009444397480006</v>
       </c>
       <c r="E4" s="34">
-        <f t="shared" ref="E4:E10" ca="1" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>3.2895509755299202E-2</v>
+        <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <v>9.0165368849657535E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.73770491803278693</v>
+        <v>0.70491803278688525</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.8385041271582001E-2</v>
+        <v>1.6446205494982522E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
         <v>232.07216445995408</v>
       </c>
       <c r="I4" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>226.15563255676793</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>225.68464703193365</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" ca="1" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-2.5494362570169848E-2</v>
+        <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <v>-2.7523841314121271E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1899,12 +1900,12 @@
         <v>0.76087748780872522</v>
       </c>
       <c r="D5" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.86819467121752325</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.72184902227872527</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.10731718340879803</v>
+        <f t="shared" si="0"/>
+        <v>-3.9028465529999945E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1912,19 +1913,19 @@
       </c>
       <c r="G5" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.4226337748676597E-2</v>
+        <v>3.4107620812836123E-2</v>
       </c>
       <c r="H5" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
         <v>250.86808983502152</v>
       </c>
       <c r="I5" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>262.48010249019137</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>261.89621866009043</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>4.6287324397480213E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.3959870832202444E-2</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -1936,32 +1937,32 @@
         <v>0.7887875467257508</v>
       </c>
       <c r="D6" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.74941840254753767</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.73183157444710967</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>-3.9369144178213134E-2</v>
+        <f t="shared" si="0"/>
+        <v>-5.6955972278641132E-2</v>
       </c>
       <c r="F6" s="35">
-        <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97266627500695713</v>
+        <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.97327656236869375</v>
       </c>
       <c r="G6" s="36">
-        <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.2666275006957162E-2</v>
+        <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>1.3276562368693789E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>218.70039150583702</v>
       </c>
       <c r="I6" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>229.18876561655594</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>229.00233127068643</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>4.7957729012291193E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.7105264393522833E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -1973,12 +1974,12 @@
         <v>0.61747392211126917</v>
       </c>
       <c r="D7" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65454664147406882</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.65658489452686997</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>3.7072719362799655E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.9110972415600798E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -1986,19 +1987,19 @@
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>4.5515142288516698E-3</v>
+        <v>6.3545518819056353E-3</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
         <v>200.75789235670646</v>
       </c>
       <c r="I7" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>195.98527386220437</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>196.24635372788543</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>-2.3773005576399022E-2</v>
+        <f t="shared" si="1"/>
+        <v>-2.2472534334067078E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2010,12 +2011,12 @@
         <v>0.63270000000000004</v>
       </c>
       <c r="D8" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.63406790042068617</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.59405152850266629</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>1.36790042068613E-3</v>
+        <f t="shared" si="0"/>
+        <v>-3.8648471497333747E-2</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2023,19 +2024,19 @@
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-8.1810566204557969E-2</v>
+        <v>-7.9910258209150944E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>146.53039613498757</v>
       </c>
       <c r="I8" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>131.11163298743858</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>132.64600764383846</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.10522569756342449</v>
+        <f t="shared" si="1"/>
+        <v>-9.4754323044062852E-2</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2047,12 +2048,12 @@
         <v>0.67570553852501991</v>
       </c>
       <c r="D9" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.67236063274389102</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.59814440235062616</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-3.3449057811288929E-3</v>
+        <f t="shared" si="0"/>
+        <v>-7.7561136174393752E-2</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2060,19 +2061,19 @@
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>-9.0761616886004173E-3</v>
+        <v>-8.8618206206812957E-3</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
         <v>149.81253801090318</v>
       </c>
       <c r="I9" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>135.60257214554579</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>134.5204081632653</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>-9.4851646290934635E-2</v>
+        <f t="shared" si="1"/>
+        <v>-0.10207510032654903</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2084,12 +2085,12 @@
         <v>0.650183652995457</v>
       </c>
       <c r="D10" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.66644558023766709</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.67352781498591241</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>1.6261927242210095E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.3344161990455414E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2097,19 +2098,19 @@
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-2.6689070279392116E-2</v>
+        <v>-2.9470943955545014E-2</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
         <v>184.92501485879896</v>
       </c>
       <c r="I10" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>189.83079459798995</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>189.35652052042698</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.6528480978827224E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.3963797785884922E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2168,8 +2169,8 @@
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f ca="1">IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>4</v>
+        <f>IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>10</v>
       </c>
       <c r="D5" s="41">
         <f>IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F4&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F4&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F4&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F4&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2180,12 +2181,12 @@
         <v>2</v>
       </c>
       <c r="F5" s="41">
-        <f ca="1">IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G5" s="42">
-        <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>3.2</v>
+        <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2194,8 +2195,8 @@
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f ca="1">IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>10</v>
+        <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-5</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2206,12 +2207,12 @@
         <v>4</v>
       </c>
       <c r="F6" s="43">
-        <f ca="1">IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G6" s="42">
-        <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>8.1999999999999993</v>
+        <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2220,24 +2221,24 @@
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f ca="1">IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-5</v>
+        <f>IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-10</v>
       </c>
       <c r="D7" s="41">
-        <f ca="1">IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
+        <f>IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>10</v>
       </c>
       <c r="E7" s="41">
-        <f ca="1">IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
+        <f>IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>2</v>
       </c>
       <c r="F7" s="41">
-        <f ca="1">IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G7" s="42">
-        <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>1.8</v>
+        <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2246,7 +2247,7 @@
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f ca="1">IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>4</v>
       </c>
       <c r="D8" s="43">
@@ -2258,11 +2259,11 @@
         <v>0</v>
       </c>
       <c r="F8" s="43">
-        <f ca="1">IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G8" s="42">
-        <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
+        <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -2272,8 +2273,8 @@
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f ca="1">IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>2</v>
+        <f>IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-5</v>
       </c>
       <c r="D9" s="41">
         <f>IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F8&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F8&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F8&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F8&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2284,12 +2285,12 @@
         <v>0</v>
       </c>
       <c r="F9" s="41">
-        <f ca="1">IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>10</v>
+        <f>IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>8</v>
       </c>
       <c r="G9" s="42">
-        <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>1.8</v>
+        <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2297,8 +2298,8 @@
         <v>7</v>
       </c>
       <c r="C10" s="43">
-        <f ca="1">IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-2</v>
+        <f>IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-10</v>
       </c>
       <c r="D10" s="43">
         <f>IF('Dati Comparti'!F9="","",IF('Dati Comparti'!F9&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F9&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F9&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F9&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F9&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2309,12 +2310,12 @@
         <v>0</v>
       </c>
       <c r="F10" s="43">
-        <f ca="1">IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>8</v>
+        <f>IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>10</v>
       </c>
       <c r="G10" s="42">
-        <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
-        <v>0</v>
+        <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
+        <v>-3</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
@@ -2322,8 +2323,8 @@
         <v>8</v>
       </c>
       <c r="C11" s="41">
-        <f ca="1">IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>2</v>
+        <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>4</v>
       </c>
       <c r="D11" s="41">
         <f>IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F10&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F10&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F10&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F10&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2334,12 +2335,12 @@
         <v>0</v>
       </c>
       <c r="F11" s="41">
-        <f ca="1">IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G11" s="42">
-        <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>1.2</v>
+        <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -2371,15 +2372,15 @@
         <v>13</v>
       </c>
       <c r="C15" s="56" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
-        <v>Editoria</v>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
+        <v>Centro Servizi</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
       <c r="G15" s="1">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>8.1999999999999993</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
+        <v>5.6</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2387,15 +2388,15 @@
         <v>14</v>
       </c>
       <c r="C16" s="55" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
+        <v>Editoria</v>
       </c>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
       <c r="F16" s="51"/>
       <c r="G16" s="2">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>3.2</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2403,14 +2404,14 @@
         <v>15</v>
       </c>
       <c r="C17" s="53" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
-        <v>Idrico</v>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
+        <v>Editoria</v>
       </c>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
       <c r="F17" s="51"/>
       <c r="G17" s="3">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -2419,15 +2420,15 @@
         <v>16</v>
       </c>
       <c r="C18" s="52" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Gori</v>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
+        <v>Medicale</v>
       </c>
       <c r="D18" s="51"/>
       <c r="E18" s="51"/>
       <c r="F18" s="51"/>
       <c r="G18" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>1.8</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2435,15 +2436,15 @@
         <v>17</v>
       </c>
       <c r="C19" s="52" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Gori</v>
       </c>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
       <c r="F19" s="51"/>
       <c r="G19" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>1.8</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2451,15 +2452,15 @@
         <v>18</v>
       </c>
       <c r="C20" s="52" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
-        <v>Medicale</v>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
+        <v>Igiene Ambientale</v>
       </c>
       <c r="D20" s="51"/>
       <c r="E20" s="51"/>
       <c r="F20" s="51"/>
       <c r="G20" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>1.2</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -2467,15 +2468,15 @@
         <v>19</v>
       </c>
       <c r="C21" s="52" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
       <c r="D21" s="51"/>
       <c r="E21" s="51"/>
       <c r="F21" s="51"/>
       <c r="G21" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
-        <v>0</v>
+        <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
+        <v>-3</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{52BA35EA-55B5-49AB-B621-9BFA023E5CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3855C0BE-F9D4-46D9-A8DF-CF5FFB2AE146}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{52BA35EA-55B5-49AB-B621-9BFA023E5CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D56AD826-4455-4E7A-BB22-0632BA68B318}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -744,6 +744,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -766,21 +781,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -948,7 +948,6 @@
           <cell r="D2" t="str">
             <v>PRODUTTIVITÀ</v>
           </cell>
-          <cell r="E2"/>
           <cell r="G2" t="str">
             <v>IUQ</v>
           </cell>
@@ -958,7 +957,6 @@
           <cell r="I2" t="str">
             <v>TMG</v>
           </cell>
-          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -991,7 +989,7 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.74009444397480006</v>
+            <v>0.74183996956118525</v>
           </cell>
           <cell r="G4">
             <v>0.70491803278688525</v>
@@ -1014,13 +1012,13 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.72184902227872527</v>
+            <v>0.72421660177961023</v>
           </cell>
           <cell r="G5">
             <v>1</v>
           </cell>
           <cell r="H5">
-            <v>3.4107620812836123E-2</v>
+            <v>3.6466512892546557E-2</v>
           </cell>
           <cell r="I5">
             <v>250.86808983502152</v>
@@ -1037,7 +1035,7 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.73183157444710967</v>
+            <v>0.7327008650058543</v>
           </cell>
           <cell r="G6">
             <v>0.97327656236869375</v>
@@ -1060,7 +1058,7 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.65658489452686997</v>
+            <v>0.66637067221735136</v>
           </cell>
           <cell r="G7">
             <v>0.69090909090909092</v>
@@ -1083,7 +1081,7 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.59405152850266629</v>
+            <v>0.58689051842799844</v>
           </cell>
           <cell r="G8">
             <v>0.36842105263157893</v>
@@ -1106,7 +1104,7 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.59814440235062616</v>
+            <v>0.6225000811784952</v>
           </cell>
           <cell r="G9">
             <v>0.5714285714285714</v>
@@ -1129,7 +1127,7 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.67352781498591241</v>
+            <v>0.69762335006827658</v>
           </cell>
           <cell r="G10">
             <v>0.21052631578947367</v>
@@ -1351,7 +1349,7 @@
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="55" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="51"/>
@@ -1426,7 +1424,7 @@
     </row>
     <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="56" t="s">
         <v>36</v>
       </c>
       <c r="C12" s="51"/>
@@ -1531,7 +1529,7 @@
     </row>
     <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="60" t="s">
+      <c r="B23" s="52" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="51"/>
@@ -1614,7 +1612,7 @@
     </row>
     <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="54" t="s">
         <v>47</v>
       </c>
       <c r="C32" s="51"/>
@@ -1697,7 +1695,7 @@
     </row>
     <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="61" t="s">
+      <c r="B41" s="53" t="s">
         <v>52</v>
       </c>
       <c r="C41" s="51"/>
@@ -1821,8 +1819,8 @@
         <v>56</v>
       </c>
       <c r="D2" s="48">
-        <f>'[1]Riepilogo mese per Commessa'!$D$1-1</f>
-        <v>46202</v>
+        <f ca="1">IF(TODAY()&gt;EOMONTH('[1]Riepilogo mese per Commessa'!$D$1,0),EOMONTH('[1]Riepilogo mese per Commessa'!$D$1,0),'[1]Riepilogo mese per Commessa'!$D$1-1)</f>
+        <v>46203</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1863,12 +1861,12 @@
         <v>0.64992907512514253</v>
       </c>
       <c r="D4" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.74009444397480006</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.74183996956118525</v>
       </c>
       <c r="E4" s="34">
-        <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>9.0165368849657535E-2</v>
+        <f t="shared" ref="E4:E10" ca="1" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <v>9.1910894436042723E-2</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1883,11 +1881,11 @@
         <v>232.07216445995408</v>
       </c>
       <c r="I4" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
         <v>225.68464703193365</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <f t="shared" ref="J4:J10" ca="1" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
         <v>-2.7523841314121271E-2</v>
       </c>
     </row>
@@ -1900,12 +1898,12 @@
         <v>0.76087748780872522</v>
       </c>
       <c r="D5" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.72184902227872527</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.72421660177961023</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" si="0"/>
-        <v>-3.9028465529999945E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-3.6660886029114992E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1913,18 +1911,18 @@
       </c>
       <c r="G5" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>3.4107620812836123E-2</v>
+        <v>3.6466512892546557E-2</v>
       </c>
       <c r="H5" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
         <v>250.86808983502152</v>
       </c>
       <c r="I5" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
         <v>261.89621866009043</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>4.3959870832202444E-2</v>
       </c>
     </row>
@@ -1937,19 +1935,19 @@
         <v>0.7887875467257508</v>
       </c>
       <c r="D6" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.73183157444710967</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.7327008650058543</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" si="0"/>
-        <v>-5.6955972278641132E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-5.6086681719896503E-2</v>
       </c>
       <c r="F6" s="35">
-        <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>0.97327656236869375</v>
       </c>
       <c r="G6" s="36">
-        <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>1.3276562368693789E-2</v>
       </c>
       <c r="H6" s="37">
@@ -1957,11 +1955,11 @@
         <v>218.70039150583702</v>
       </c>
       <c r="I6" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>229.00233127068643</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>4.7105264393522833E-2</v>
       </c>
     </row>
@@ -1974,12 +1972,12 @@
         <v>0.61747392211126917</v>
       </c>
       <c r="D7" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65658489452686997</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.66637067221735136</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" si="0"/>
-        <v>3.9110972415600798E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4.8896750106082187E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -1994,11 +1992,11 @@
         <v>200.75789235670646</v>
       </c>
       <c r="I7" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
         <v>196.24635372788543</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-2.2472534334067078E-2</v>
       </c>
     </row>
@@ -2011,12 +2009,12 @@
         <v>0.63270000000000004</v>
       </c>
       <c r="D8" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.59405152850266629</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.58689051842799844</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" si="0"/>
-        <v>-3.8648471497333747E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-4.5809481572001598E-2</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2031,11 +2029,11 @@
         <v>146.53039613498757</v>
       </c>
       <c r="I8" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>132.64600764383846</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-9.4754323044062852E-2</v>
       </c>
     </row>
@@ -2048,12 +2046,12 @@
         <v>0.67570553852501991</v>
       </c>
       <c r="D9" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.59814440235062616</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.6225000811784952</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" si="0"/>
-        <v>-7.7561136174393752E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>-5.3205457346524709E-2</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2068,11 +2066,11 @@
         <v>149.81253801090318</v>
       </c>
       <c r="I9" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
         <v>134.5204081632653</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>-0.10207510032654903</v>
       </c>
     </row>
@@ -2085,12 +2083,12 @@
         <v>0.650183652995457</v>
       </c>
       <c r="D10" s="33">
-        <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.67352781498591241</v>
+        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.69762335006827658</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" si="0"/>
-        <v>2.3344161990455414E-2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4.7439697072819587E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2105,11 +2103,11 @@
         <v>184.92501485879896</v>
       </c>
       <c r="I10" s="37">
-        <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
         <v>189.35652052042698</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>2.3963797785884922E-2</v>
       </c>
     </row>
@@ -2169,7 +2167,7 @@
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f>IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>10</v>
       </c>
       <c r="D5" s="41">
@@ -2181,11 +2179,11 @@
         <v>2</v>
       </c>
       <c r="F5" s="41">
-        <f>IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G5" s="42">
-        <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
         <v>5.6</v>
       </c>
     </row>
@@ -2195,7 +2193,7 @@
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-5</v>
       </c>
       <c r="D6" s="43">
@@ -2207,11 +2205,11 @@
         <v>4</v>
       </c>
       <c r="F6" s="43">
-        <f>IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G6" s="42">
-        <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -2221,23 +2219,23 @@
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f>IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D7" s="41">
-        <f>IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
+        <f ca="1">IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>10</v>
       </c>
       <c r="E7" s="41">
-        <f>IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
+        <f ca="1">IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>2</v>
       </c>
       <c r="F7" s="41">
-        <f>IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G7" s="42">
-        <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
         <v>-0.2</v>
       </c>
     </row>
@@ -2247,8 +2245,8 @@
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>4</v>
+        <f ca="1">IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>6</v>
       </c>
       <c r="D8" s="43">
         <f>IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F7&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F7&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F7&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F7&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2259,12 +2257,12 @@
         <v>0</v>
       </c>
       <c r="F8" s="43">
-        <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G8" s="42">
-        <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>2.2000000000000002</v>
+        <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2273,8 +2271,8 @@
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f>IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-5</v>
+        <f ca="1">IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>-10</v>
       </c>
       <c r="D9" s="41">
         <f>IF('Dati Comparti'!F8="","",IF('Dati Comparti'!F8&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F8&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F8&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F8&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F8&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2285,12 +2283,12 @@
         <v>0</v>
       </c>
       <c r="F9" s="41">
-        <f>IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>8</v>
       </c>
       <c r="G9" s="42">
-        <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>-1.2</v>
+        <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2298,7 +2296,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="43">
-        <f>IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f ca="1">IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D10" s="43">
@@ -2310,11 +2308,11 @@
         <v>0</v>
       </c>
       <c r="F10" s="43">
-        <f>IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>10</v>
       </c>
       <c r="G10" s="42">
-        <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
+        <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
         <v>-3</v>
       </c>
     </row>
@@ -2323,8 +2321,8 @@
         <v>8</v>
       </c>
       <c r="C11" s="41">
-        <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>4</v>
+        <f ca="1">IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>6</v>
       </c>
       <c r="D11" s="41">
         <f>IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F10&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F10&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F10&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F10&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2335,16 +2333,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="41">
-        <f>IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f ca="1">IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G11" s="42">
-        <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>2</v>
+        <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="62" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="51"/>
@@ -2357,12 +2355,12 @@
       <c r="B14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="63" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
-      <c r="F14" s="59"/>
+      <c r="F14" s="64"/>
       <c r="G14" s="14" t="s">
         <v>12</v>
       </c>
@@ -2371,15 +2369,15 @@
       <c r="B15" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="56" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
+      <c r="C15" s="61" t="str">
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Centro Servizi</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
       <c r="G15" s="1">
-        <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
         <v>5.6</v>
       </c>
     </row>
@@ -2387,63 +2385,63 @@
       <c r="B16" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="55" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Editoria</v>
+      <c r="C16" s="60" t="str">
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
+        <v>Idrico</v>
       </c>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
       <c r="F16" s="51"/>
       <c r="G16" s="2">
-        <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>2.2000000000000002</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="53" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
-        <v>Editoria</v>
+      <c r="C17" s="58" t="str">
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
+        <v>Medicale</v>
       </c>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
       <c r="F17" s="51"/>
       <c r="G17" s="3">
-        <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>2.2000000000000002</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="52" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Medicale</v>
+      <c r="C18" s="57" t="str">
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
+        <v>Editoria</v>
       </c>
       <c r="D18" s="51"/>
       <c r="E18" s="51"/>
       <c r="F18" s="51"/>
       <c r="G18" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>2</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="52" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
+      <c r="C19" s="57" t="str">
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Gori</v>
       </c>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
       <c r="F19" s="51"/>
       <c r="G19" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
         <v>-0.2</v>
       </c>
     </row>
@@ -2451,36 +2449,36 @@
       <c r="B20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="52" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
-        <v>Igiene Ambientale</v>
+      <c r="C20" s="57" t="str">
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
+        <v>ITS</v>
       </c>
       <c r="D20" s="51"/>
       <c r="E20" s="51"/>
       <c r="F20" s="51"/>
       <c r="G20" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-1.2</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
+        <v>-3</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="52" t="str">
-        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
-        <v>ITS</v>
+      <c r="C21" s="57" t="str">
+        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
+        <v>Igiene Ambientale</v>
       </c>
       <c r="D21" s="51"/>
       <c r="E21" s="51"/>
       <c r="F21" s="51"/>
       <c r="G21" s="4">
-        <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
-        <v>-3</v>
+        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="59" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="51"/>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{52BA35EA-55B5-49AB-B621-9BFA023E5CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D56AD826-4455-4E7A-BB22-0632BA68B318}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{52BA35EA-55B5-49AB-B621-9BFA023E5CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{716D26E4-AF52-4F40-A285-2AF977767B98}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -744,21 +744,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -781,6 +766,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -869,9 +869,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="db iniziale"/>
       <sheetName val="Code_Commesse"/>
@@ -887,9 +884,6 @@
       <sheetName val="Stati barra CS"/>
       <sheetName val="export chiamate GORI"/>
       <sheetName val="GORI"/>
-      <sheetName val="chiamate NET Udine INB"/>
-      <sheetName val="chiamate NET Udine OUT"/>
-      <sheetName val="Abbandonate NET Udine"/>
       <sheetName val="QUERY - Mese corrente"/>
       <sheetName val="Riepilogo mese per Commessa"/>
       <sheetName val="Riepilogo old"/>
@@ -905,7 +899,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="B1">
-            <v>46174</v>
+            <v>46204</v>
           </cell>
         </row>
       </sheetData>
@@ -923,24 +917,21 @@
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
+      <sheetData sheetId="15">
+        <row r="1">
+          <cell r="D1">
+            <v>46234</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
-      <sheetData sheetId="18">
-        <row r="1">
-          <cell r="D1">
-            <v>46203</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26">
+      <sheetData sheetId="23">
         <row r="2">
           <cell r="B2" t="str">
             <v>CHIAVE</v>
@@ -948,6 +939,7 @@
           <cell r="D2" t="str">
             <v>PRODUTTIVITÀ</v>
           </cell>
+          <cell r="E2"/>
           <cell r="G2" t="str">
             <v>IUQ</v>
           </cell>
@@ -957,6 +949,7 @@
           <cell r="I2" t="str">
             <v>TMG</v>
           </cell>
+          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="B3" t="str">
@@ -989,19 +982,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.74183996956118525</v>
+            <v>0.80149221026666073</v>
           </cell>
           <cell r="G4">
-            <v>0.70491803278688525</v>
+            <v>0.59677419354838712</v>
           </cell>
           <cell r="H4">
-            <v>1.6446205494982522E-2</v>
+            <v>-6.1060812979539681E-3</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>225.68464703193365</v>
+            <v>228.67883384688315</v>
           </cell>
         </row>
         <row r="5">
@@ -1012,7 +1005,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.72421660177961023</v>
+            <v>0.87479674723381418</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1024,7 +1017,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>261.89621866009043</v>
+            <v>289.03211253485387</v>
           </cell>
         </row>
         <row r="6">
@@ -1035,19 +1028,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.7327008650058543</v>
+            <v>0.71961844766054561</v>
           </cell>
           <cell r="G6">
-            <v>0.97327656236869375</v>
+            <v>0.97646774712890416</v>
           </cell>
           <cell r="H6">
-            <v>1.3276562368693789E-2</v>
+            <v>1.6467747128904198E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>229.00233127068643</v>
+            <v>218.60295127916243</v>
           </cell>
         </row>
         <row r="7">
@@ -1058,19 +1051,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.66637067221735136</v>
+            <v>0.66428523700309672</v>
           </cell>
           <cell r="G7">
-            <v>0.69090909090909092</v>
+            <v>0.6964285714285714</v>
           </cell>
           <cell r="H7">
-            <v>6.3545518819056353E-3</v>
+            <v>-1.7846323305115881E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>196.24635372788543</v>
+            <v>200.90312019693354</v>
           </cell>
         </row>
         <row r="8">
@@ -1081,19 +1074,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.58689051842799844</v>
+            <v>0.49564045920643385</v>
           </cell>
           <cell r="G8">
-            <v>0.36842105263157893</v>
+            <v>0.52941176470588236</v>
           </cell>
           <cell r="H8">
-            <v>-7.9910258209150944E-2</v>
+            <v>-4.3672220101830597E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>132.64600764383846</v>
+            <v>262.65059588299027</v>
           </cell>
         </row>
         <row r="9">
@@ -1104,19 +1097,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.6225000811784952</v>
+            <v>0.62773305843263116</v>
           </cell>
           <cell r="G9">
-            <v>0.5714285714285714</v>
+            <v>0.5</v>
           </cell>
           <cell r="H9">
-            <v>-8.8618206206812957E-3</v>
+            <v>-6.0680839368606292E-3</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>134.5204081632653</v>
+            <v>136.0919742237844</v>
           </cell>
         </row>
         <row r="10">
@@ -1127,19 +1120,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.69762335006827658</v>
+            <v>0.69731645522512009</v>
           </cell>
           <cell r="G10">
-            <v>0.21052631578947367</v>
+            <v>0.41463414634146339</v>
           </cell>
           <cell r="H10">
-            <v>-2.9470943955545014E-2</v>
+            <v>-7.0113275574709682E-3</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>189.35652052042698</v>
+            <v>195.32856366206371</v>
           </cell>
         </row>
       </sheetData>
@@ -1328,34 +1321,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:D48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2" style="5" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="8.7109375" style="5"/>
+    <col min="6" max="6" width="8.6640625" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="51"/>
     </row>
-    <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="55" t="s">
+    <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="63" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="51"/>
       <c r="D4" s="51"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="14" t="s">
         <v>23</v>
       </c>
@@ -1366,7 +1359,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
         <v>26</v>
       </c>
@@ -1377,7 +1370,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="17" t="s">
         <v>28</v>
       </c>
@@ -1388,7 +1381,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="18" t="s">
         <v>30</v>
       </c>
@@ -1399,7 +1392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="19" t="s">
         <v>32</v>
       </c>
@@ -1410,7 +1403,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
         <v>34</v>
       </c>
@@ -1422,15 +1415,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="56" t="s">
+    <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="64" t="s">
         <v>36</v>
       </c>
       <c r="C12" s="51"/>
       <c r="D12" s="51"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="14" t="s">
         <v>37</v>
       </c>
@@ -1441,7 +1434,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="21" t="s">
         <v>40</v>
       </c>
@@ -1450,7 +1443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="23">
         <v>0.06</v>
       </c>
@@ -1461,7 +1454,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="23">
         <v>0.04</v>
       </c>
@@ -1472,7 +1465,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="23">
         <v>0.02</v>
       </c>
@@ -1483,7 +1476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="23">
         <v>0</v>
       </c>
@@ -1494,7 +1487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="24">
         <v>-1.9E-2</v>
       </c>
@@ -1505,7 +1498,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="24">
         <v>-3.9E-2</v>
       </c>
@@ -1516,7 +1509,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" s="24" t="s">
         <v>41</v>
       </c>
@@ -1527,15 +1520,15 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="52" t="s">
+    <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="60" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="14" t="s">
         <v>43</v>
       </c>
@@ -1546,7 +1539,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" s="21" t="s">
         <v>45</v>
       </c>
@@ -1557,7 +1550,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B26" s="23">
         <v>0.9</v>
       </c>
@@ -1568,7 +1561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" s="23">
         <v>0.85</v>
       </c>
@@ -1579,7 +1572,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B28" s="25">
         <v>0.8</v>
       </c>
@@ -1590,7 +1583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" s="25">
         <v>0.7</v>
       </c>
@@ -1601,7 +1594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B30" s="26"/>
       <c r="C30" s="24">
         <v>0.69989999999999997</v>
@@ -1610,15 +1603,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="54" t="s">
+    <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B32" s="62" t="s">
         <v>47</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="51"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="14" t="s">
         <v>48</v>
       </c>
@@ -1629,7 +1622,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="21" t="s">
         <v>50</v>
       </c>
@@ -1638,7 +1631,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="23">
         <v>8.1000000000000003E-2</v>
       </c>
@@ -1649,7 +1642,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="23">
         <v>5.0999999999999997E-2</v>
       </c>
@@ -1660,7 +1653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="25">
         <v>3.1E-2</v>
       </c>
@@ -1671,7 +1664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B38" s="25">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -1682,7 +1675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="24" t="s">
         <v>51</v>
       </c>
@@ -1693,15 +1686,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="53" t="s">
+    <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B41" s="61" t="s">
         <v>52</v>
       </c>
       <c r="C41" s="51"/>
       <c r="D41" s="51"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="14" t="s">
         <v>37</v>
       </c>
@@ -1712,7 +1705,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" s="21" t="s">
         <v>53</v>
       </c>
@@ -1723,7 +1716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B44" s="23">
         <v>-9.9000000000000005E-2</v>
       </c>
@@ -1734,7 +1727,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B45" s="23">
         <v>-4.9000000000000002E-2</v>
       </c>
@@ -1745,7 +1738,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B46" s="25">
         <v>0</v>
       </c>
@@ -1756,7 +1749,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B47" s="25">
         <v>0.05</v>
       </c>
@@ -1767,7 +1760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B48" s="24">
         <v>0.1</v>
       </c>
@@ -1795,35 +1788,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:J10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="5" customWidth="1"/>
     <col min="2" max="2" width="22" style="5" customWidth="1"/>
     <col min="3" max="10" width="16" style="5" customWidth="1"/>
     <col min="11" max="11" width="2" style="5" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="8.7109375" style="5"/>
+    <col min="12" max="12" width="8.6640625" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C1" s="47" t="s">
         <v>55</v>
       </c>
       <c r="D1" s="49">
         <f>'[1]db iniziale'!$B$1</f>
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2" s="47" t="s">
         <v>56</v>
       </c>
       <c r="D2" s="48">
         <f ca="1">IF(TODAY()&gt;EOMONTH('[1]Riepilogo mese per Commessa'!$D$1,0),EOMONTH('[1]Riepilogo mese per Commessa'!$D$1,0),'[1]Riepilogo mese per Commessa'!$D$1-1)</f>
-        <v>46203</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
@@ -1852,7 +1845,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="32" t="s">
         <v>65</v>
       </c>
@@ -1861,35 +1854,35 @@
         <v>0.64992907512514253</v>
       </c>
       <c r="D4" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.74183996956118525</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.80149221026666073</v>
       </c>
       <c r="E4" s="34">
-        <f t="shared" ref="E4:E10" ca="1" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>9.1910894436042723E-2</v>
+        <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
+        <v>0.1515631351415182</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.70491803278688525</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.6446205494982522E-2</v>
+        <v>-6.1060812979539681E-3</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
         <v>232.07216445995408</v>
       </c>
       <c r="I4" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>225.68464703193365</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
+        <v>228.67883384688315</v>
       </c>
       <c r="J4" s="34">
-        <f t="shared" ref="J4:J10" ca="1" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-2.7523841314121271E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
+        <v>-1.4621876867341737E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="38" t="s">
         <v>66</v>
       </c>
@@ -1898,12 +1891,12 @@
         <v>0.76087748780872522</v>
       </c>
       <c r="D5" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.72421660177961023</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.87479674723381418</v>
       </c>
       <c r="E5" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-3.6660886029114992E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.11391925942508896</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1918,15 +1911,15 @@
         <v>250.86808983502152</v>
       </c>
       <c r="I5" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>261.89621866009043</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
+        <v>289.03211253485387</v>
       </c>
       <c r="J5" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>4.3959870832202444E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0.15212784824459008</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="32" t="s">
         <v>67</v>
       </c>
@@ -1935,35 +1928,35 @@
         <v>0.7887875467257508</v>
       </c>
       <c r="D6" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.7327008650058543</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.71961844766054561</v>
       </c>
       <c r="E6" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>-5.6086681719896503E-2</v>
+        <f t="shared" si="0"/>
+        <v>-6.9169099065205186E-2</v>
       </c>
       <c r="F6" s="35">
-        <f ca="1">INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97327656236869375</v>
+        <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.97646774712890416</v>
       </c>
       <c r="G6" s="36">
-        <f ca="1">INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.3276562368693789E-2</v>
+        <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>1.6467747128904198E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
         <v>218.70039150583702</v>
       </c>
       <c r="I6" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>229.00233127068643</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
+        <v>218.60295127916243</v>
       </c>
       <c r="J6" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>4.7105264393522833E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-4.4554207701083147E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="38" t="s">
         <v>68</v>
       </c>
@@ -1972,35 +1965,35 @@
         <v>0.61747392211126917</v>
       </c>
       <c r="D7" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.66637067221735136</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.66428523700309672</v>
       </c>
       <c r="E7" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.8896750106082187E-2</v>
+        <f t="shared" si="0"/>
+        <v>4.6811314891827549E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.69090909090909092</v>
+        <v>0.6964285714285714</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>6.3545518819056353E-3</v>
+        <v>-1.7846323305115881E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
         <v>200.75789235670646</v>
       </c>
       <c r="I7" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>196.24635372788543</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
+        <v>200.90312019693354</v>
       </c>
       <c r="J7" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>-2.2472534334067078E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>7.2339791239209924E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
         <v>69</v>
       </c>
@@ -2009,35 +2002,35 @@
         <v>0.63270000000000004</v>
       </c>
       <c r="D8" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.58689051842799844</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.49564045920643385</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>-4.5809481572001598E-2</v>
+        <f t="shared" si="0"/>
+        <v>-0.13705954079356619</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.36842105263157893</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-7.9910258209150944E-2</v>
+        <v>-4.3672220101830597E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
         <v>146.53039613498757</v>
       </c>
       <c r="I8" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>132.64600764383846</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
+        <v>262.65059588299027</v>
       </c>
       <c r="J8" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>-9.4754323044062852E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0.79246492748869513</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="38" t="s">
         <v>7</v>
       </c>
@@ -2046,35 +2039,35 @@
         <v>0.67570553852501991</v>
       </c>
       <c r="D9" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.6225000811784952</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.62773305843263116</v>
       </c>
       <c r="E9" s="39">
-        <f t="shared" ca="1" si="0"/>
-        <v>-5.3205457346524709E-2</v>
+        <f t="shared" si="0"/>
+        <v>-4.7972480092388747E-2</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>-8.8618206206812957E-3</v>
+        <v>-6.0680839368606292E-3</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
         <v>149.81253801090318</v>
       </c>
       <c r="I9" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>134.5204081632653</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
+        <v>136.0919742237844</v>
       </c>
       <c r="J9" s="39">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.10207510032654903</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-9.1584883143226714E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="32" t="s">
         <v>8</v>
       </c>
@@ -2083,32 +2076,32 @@
         <v>0.650183652995457</v>
       </c>
       <c r="D10" s="33">
-        <f ca="1">INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.69762335006827658</v>
+        <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>0.69731645522512009</v>
       </c>
       <c r="E10" s="34">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.7439697072819587E-2</v>
+        <f t="shared" si="0"/>
+        <v>4.7132802229663096E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.21052631578947367</v>
+        <v>0.41463414634146339</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-2.9470943955545014E-2</v>
+        <v>-7.0113275574709682E-3</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
         <v>184.92501485879896</v>
       </c>
       <c r="I10" s="37">
-        <f ca="1">INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>189.35652052042698</v>
+        <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
+        <v>195.32856366206371</v>
       </c>
       <c r="J10" s="34">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.3963797785884922E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.6258201797136378E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2120,18 +2113,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:G23"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="5" customWidth="1"/>
     <col min="2" max="2" width="22" style="5" customWidth="1"/>
     <col min="3" max="6" width="14" style="5" customWidth="1"/>
     <col min="7" max="7" width="18" style="5" customWidth="1"/>
     <col min="8" max="8" width="2" style="5" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="8.7109375" style="5"/>
+    <col min="9" max="9" width="8.6640625" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="50" t="s">
         <v>0</v>
       </c>
@@ -2141,7 +2134,7 @@
       <c r="F2" s="51"/>
       <c r="G2" s="51"/>
     </row>
-    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="27" t="s">
         <v>1</v>
       </c>
@@ -2161,40 +2154,40 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="32" t="str">
         <f>'Dati Comparti'!B4</f>
         <v>Centro Servizi</v>
       </c>
       <c r="C5" s="41">
-        <f ca="1">IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E4="","",IF('Dati Comparti'!E4&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E4&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E4&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E4&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E4&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E4&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E4&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>10</v>
       </c>
       <c r="D5" s="41">
         <f>IF('Dati Comparti'!F4="","",IF('Dati Comparti'!F4&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F4&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F4&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F4&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F4&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="41">
         <f>IF('Dati Comparti'!G4="","",IF('Dati Comparti'!G4&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G4&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G4&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G4&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G4&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="41">
-        <f ca="1">IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>6</v>
       </c>
       <c r="G5" s="42">
-        <f ca="1">IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+        <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="38" t="str">
         <f>'Dati Comparti'!B5</f>
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
-        <f ca="1">IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-5</v>
+        <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <v>10</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2205,47 +2198,47 @@
         <v>4</v>
       </c>
       <c r="F6" s="43">
-        <f ca="1">IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>4</v>
+        <f>IF('Dati Comparti'!J5="","",IF('Dati Comparti'!J5&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J5&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J5&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J5&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J5&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>0</v>
       </c>
       <c r="G6" s="42">
-        <f ca="1">IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+        <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="32" t="str">
         <f>'Dati Comparti'!B6</f>
         <v>Gori</v>
       </c>
       <c r="C7" s="41">
-        <f ca="1">IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D7" s="41">
-        <f ca="1">IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
+        <f>IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
         <v>10</v>
       </c>
       <c r="E7" s="41">
-        <f ca="1">IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
+        <f>IF('Dati Comparti'!G6="","",IF('Dati Comparti'!G6&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G6&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G6&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G6&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G6&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
         <v>2</v>
       </c>
       <c r="F7" s="41">
-        <f ca="1">IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <f>IF('Dati Comparti'!J6="","",IF('Dati Comparti'!J6&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J6&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J6&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J6&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J6&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
         <v>4</v>
       </c>
       <c r="G7" s="42">
-        <f ca="1">IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
+        <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
         <v>-0.2</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="38" t="str">
         <f>'Dati Comparti'!B7</f>
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
-        <f ca="1">IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>6</v>
       </c>
       <c r="D8" s="43">
@@ -2257,21 +2250,21 @@
         <v>0</v>
       </c>
       <c r="F8" s="43">
-        <f ca="1">IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>6</v>
+        <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>4</v>
       </c>
       <c r="G8" s="42">
-        <f ca="1">IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+        <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="32" t="str">
         <f>'Dati Comparti'!B8</f>
         <v>Igiene Ambientale</v>
       </c>
       <c r="C9" s="41">
-        <f ca="1">IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E8="","",IF('Dati Comparti'!E8&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E8&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E8&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E8&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E8&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E8&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E8&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D9" s="41">
@@ -2283,20 +2276,20 @@
         <v>0</v>
       </c>
       <c r="F9" s="41">
-        <f ca="1">IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>8</v>
+        <f>IF('Dati Comparti'!J8="","",IF('Dati Comparti'!J8&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J8&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J8&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J8&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J8&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>0</v>
       </c>
       <c r="G9" s="42">
-        <f ca="1">IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+        <f>IF(OR(C9="",D9="",E9="",F9=""),"",ROUND(C9*Parametri!C6+D9*Parametri!C7+E9*Parametri!C8+F9*Parametri!C9,2))</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="38" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="43">
-        <f ca="1">IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E9="","",IF('Dati Comparti'!E9&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E9&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E9&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E9&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E9&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E9&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E9&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>-10</v>
       </c>
       <c r="D10" s="43">
@@ -2308,20 +2301,20 @@
         <v>0</v>
       </c>
       <c r="F10" s="43">
-        <f ca="1">IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>10</v>
+        <f>IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>8</v>
       </c>
       <c r="G10" s="42">
-        <f ca="1">IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+        <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="32" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="41">
-        <f ca="1">IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
+        <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
         <v>6</v>
       </c>
       <c r="D11" s="41">
@@ -2333,16 +2326,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="41">
-        <f ca="1">IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>4</v>
+        <f>IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
+        <v>2</v>
       </c>
       <c r="G11" s="42">
-        <f ca="1">IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="62" t="s">
+        <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="57" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="51"/>
@@ -2351,134 +2344,134 @@
       <c r="F13" s="51"/>
       <c r="G13" s="51"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="58" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
-      <c r="F14" s="64"/>
+      <c r="F14" s="59"/>
       <c r="G14" s="14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="61" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+      <c r="C15" s="56" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
+        <v>Editoria</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
       <c r="G15" s="1">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="60" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Idrico</v>
+      <c r="C16" s="55" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
+        <v>Centro Servizi</v>
       </c>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
       <c r="F16" s="51"/>
       <c r="G16" s="2">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="58" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
-        <v>Medicale</v>
+      <c r="C17" s="53" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
+        <v>Idrico</v>
       </c>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
       <c r="F17" s="51"/>
       <c r="G17" s="3">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
         <v>2.8</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Editoria</v>
+      <c r="C18" s="52" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
+        <v>Medicale</v>
       </c>
       <c r="D18" s="51"/>
       <c r="E18" s="51"/>
       <c r="F18" s="51"/>
       <c r="G18" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
+      <c r="C19" s="52" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Gori</v>
       </c>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
       <c r="F19" s="51"/>
       <c r="G19" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
+        <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
         <v>-0.2</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
+      <c r="C20" s="52" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
       <c r="D20" s="51"/>
       <c r="E20" s="51"/>
       <c r="F20" s="51"/>
       <c r="G20" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="57" t="str">
-        <f ca="1">IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
+      <c r="C21" s="52" t="str">
+        <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>Igiene Ambientale</v>
       </c>
       <c r="D21" s="51"/>
       <c r="E21" s="51"/>
       <c r="F21" s="51"/>
       <c r="G21" s="4">
-        <f ca="1">IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="59" t="s">
+        <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="54" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="51"/>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{52BA35EA-55B5-49AB-B621-9BFA023E5CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{716D26E4-AF52-4F40-A285-2AF977767B98}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB304AE1-355A-4844-9A9B-56A687F65D85}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,13 @@
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
     <sheet name="Dati Comparti" sheetId="2" r:id="rId2"/>
     <sheet name="Scoring" sheetId="3" r:id="rId3"/>
+    <sheet name="Storico" sheetId="4" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="74">
   <si>
     <t>🏆  SCORING COMPARTI</t>
   </si>
@@ -261,6 +263,18 @@
   </si>
   <si>
     <t>Igiene Ambientale</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
   </si>
 </sst>
 </file>
@@ -272,7 +286,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="mmmm\ yyyy"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,8 +409,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -511,8 +535,13 @@
         <bgColor rgb="FFFADBD8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF507E22"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -587,11 +616,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDDE6CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFEEF3E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFEEF3E3"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -739,6 +797,13 @@
     </xf>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -780,6 +845,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -899,7 +968,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="B1">
-            <v>46204</v>
+            <v>46235</v>
           </cell>
         </row>
       </sheetData>
@@ -920,7 +989,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46234</v>
+            <v>46244</v>
           </cell>
         </row>
       </sheetData>
@@ -982,19 +1051,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.80149221026666073</v>
+            <v>0.86899050100283048</v>
           </cell>
           <cell r="G4">
-            <v>0.59677419354838712</v>
+            <v>0.53333333333333333</v>
           </cell>
           <cell r="H4">
-            <v>-6.1060812979539681E-3</v>
+            <v>-3.3796156183765171E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>228.67883384688315</v>
+            <v>220.71247436136491</v>
           </cell>
         </row>
         <row r="5">
@@ -1005,7 +1074,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.87479674723381418</v>
+            <v>0.89382430001142776</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1017,7 +1086,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>289.03211253485387</v>
+            <v>304.39368474662592</v>
           </cell>
         </row>
         <row r="6">
@@ -1028,19 +1097,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.71961844766054561</v>
+            <v>1.0921435016397814</v>
           </cell>
           <cell r="G6">
-            <v>0.97646774712890416</v>
+            <v>0.97463768115942029</v>
           </cell>
           <cell r="H6">
-            <v>1.6467747128904198E-2</v>
+            <v>1.4637681159420324E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>218.60295127916243</v>
+            <v>224.67750929368029</v>
           </cell>
         </row>
         <row r="7">
@@ -1051,19 +1120,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.66428523700309672</v>
+            <v>0.65799697583622063</v>
           </cell>
           <cell r="G7">
-            <v>0.6964285714285714</v>
+            <v>0.48214285714285715</v>
           </cell>
           <cell r="H7">
-            <v>-1.7846323305115881E-2</v>
+            <v>-5.9696272323367293E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>200.90312019693354</v>
+            <v>193.61581454121307</v>
           </cell>
         </row>
         <row r="8">
@@ -1074,19 +1143,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.49564045920643385</v>
+            <v>0.46901751304228245</v>
           </cell>
           <cell r="G8">
-            <v>0.52941176470588236</v>
+            <v>0.3125</v>
           </cell>
           <cell r="H8">
-            <v>-4.3672220101830597E-2</v>
+            <v>-5.7467116796869694E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>262.65059588299027</v>
+            <v>250.88470588235293</v>
           </cell>
         </row>
         <row r="9">
@@ -1097,19 +1166,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.62773305843263116</v>
+            <v>0.47854522084832635</v>
           </cell>
           <cell r="G9">
-            <v>0.5</v>
+            <v>0.75</v>
           </cell>
           <cell r="H9">
-            <v>-6.0680839368606292E-3</v>
+            <v>1.1361136265038253E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>136.0919742237844</v>
+            <v>141.72474747474749</v>
           </cell>
         </row>
         <row r="10">
@@ -1120,19 +1189,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.69731645522512009</v>
+            <v>0.80676622784243623</v>
           </cell>
           <cell r="G10">
-            <v>0.41463414634146339</v>
+            <v>0.3611111111111111</v>
           </cell>
           <cell r="H10">
-            <v>-7.0113275574709682E-3</v>
+            <v>-1.1831147902635845E-2</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>195.32856366206371</v>
+            <v>201.43980181668044</v>
           </cell>
         </row>
       </sheetData>
@@ -1334,19 +1403,19 @@
   <sheetData>
     <row r="1" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="14" t="s">
@@ -1417,11 +1486,11 @@
     </row>
     <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="14" t="s">
@@ -1522,11 +1591,11 @@
     </row>
     <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="60" t="s">
+      <c r="B23" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="14" t="s">
@@ -1605,11 +1674,11 @@
     </row>
     <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="14" t="s">
@@ -1688,11 +1757,11 @@
     </row>
     <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="61" t="s">
+      <c r="B41" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="14" t="s">
@@ -1804,7 +1873,7 @@
       </c>
       <c r="D1" s="49">
         <f>'[1]db iniziale'!$B$1</f>
-        <v>46204</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
@@ -1812,8 +1881,8 @@
         <v>56</v>
       </c>
       <c r="D2" s="48">
-        <f ca="1">IF(TODAY()&gt;EOMONTH('[1]Riepilogo mese per Commessa'!$D$1,0),EOMONTH('[1]Riepilogo mese per Commessa'!$D$1,0),'[1]Riepilogo mese per Commessa'!$D$1-1)</f>
-        <v>46234</v>
+        <f>'[1]Riepilogo mese per Commessa'!$D$1-1</f>
+        <v>46243</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1855,19 +1924,19 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.80149221026666073</v>
+        <v>0.86899050100283048</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>0.1515631351415182</v>
+        <v>0.21906142587768795</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.59677419354838712</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>-6.1060812979539681E-3</v>
+        <v>-3.3796156183765171E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1875,11 +1944,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>228.67883384688315</v>
+        <v>220.71247436136491</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-1.4621876867341737E-2</v>
+        <v>-4.8948955705324905E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
@@ -1892,11 +1961,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.87479674723381418</v>
+        <v>0.89382430001142776</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>0.11391925942508896</v>
+        <v>0.13294681220270255</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1912,11 +1981,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>289.03211253485387</v>
+        <v>304.39368474662592</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>0.15212784824459008</v>
+        <v>0.21336151180807594</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -1929,19 +1998,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.71961844766054561</v>
+        <v>1.0921435016397814</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>-6.9169099065205186E-2</v>
+        <v>0.30335595491403056</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97646774712890416</v>
+        <v>0.97463768115942029</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.6467747128904198E-2</v>
+        <v>1.4637681159420324E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -1949,11 +2018,11 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>218.60295127916243</v>
+        <v>224.67750929368029</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="1"/>
-        <v>-4.4554207701083147E-4</v>
+        <v>2.7330165011084321E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
@@ -1966,19 +2035,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.66428523700309672</v>
+        <v>0.65799697583622063</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>4.6811314891827549E-2</v>
+        <v>4.0523053724951463E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.6964285714285714</v>
+        <v>0.48214285714285715</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>-1.7846323305115881E-2</v>
+        <v>-5.9696272323367293E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -1986,11 +2055,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>200.90312019693354</v>
+        <v>193.61581454121307</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>7.2339791239209924E-4</v>
+        <v>-3.5575576788798698E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
@@ -2003,19 +2072,19 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.49564045920643385</v>
+        <v>0.46901751304228245</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.13705954079356619</v>
+        <v>-0.16368248695771759</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.52941176470588236</v>
+        <v>0.3125</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-4.3672220101830597E-2</v>
+        <v>-5.7467116796869694E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2023,11 +2092,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>262.65059588299027</v>
+        <v>250.88470588235293</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.79246492748869513</v>
+        <v>0.71216834527104866</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
@@ -2040,19 +2109,19 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.62773305843263116</v>
+        <v>0.47854522084832635</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-4.7972480092388747E-2</v>
+        <v>-0.19716031767669356</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>-6.0680839368606292E-3</v>
+        <v>1.1361136265038253E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2060,11 +2129,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>136.0919742237844</v>
+        <v>141.72474747474749</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>-9.1584883143226714E-2</v>
+        <v>-5.3986072484581191E-2</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
@@ -2077,19 +2146,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.69731645522512009</v>
+        <v>0.80676622784243623</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>4.7132802229663096E-2</v>
+        <v>0.15658257484697924</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.41463414634146339</v>
+        <v>0.3611111111111111</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-7.0113275574709682E-3</v>
+        <v>-1.1831147902635845E-2</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2097,11 +2166,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>195.32856366206371</v>
+        <v>201.43980181668044</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>5.6258201797136378E-2</v>
+        <v>8.9305316376432284E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2125,14 +2194,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
     </row>
     <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="27" t="s">
@@ -2213,7 +2282,7 @@
       </c>
       <c r="C7" s="41">
         <f>IF('Dati Comparti'!E6="","",IF('Dati Comparti'!E6&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E6&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E6&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E6&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E6&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E6&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E6&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="D7" s="41">
         <f>IF('Dati Comparti'!F6="","",IF('Dati Comparti'!F6&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F6&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F6&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F6&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F6&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2229,7 +2298,7 @@
       </c>
       <c r="G7" s="42">
         <f>IF(OR(C7="",D7="",E7="",F7=""),"",ROUND(C7*Parametri!C6+D7*Parametri!C7+E7*Parametri!C8+F7*Parametri!C9,2))</f>
-        <v>-0.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -2251,11 +2320,11 @@
       </c>
       <c r="F8" s="43">
         <f>IF('Dati Comparti'!J7="","",IF('Dati Comparti'!J7&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J7&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J7&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J7&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J7&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G8" s="42">
         <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -2294,11 +2363,11 @@
       </c>
       <c r="D10" s="43">
         <f>IF('Dati Comparti'!F9="","",IF('Dati Comparti'!F9&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F9&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F9&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F9&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F9&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="43">
         <f>IF('Dati Comparti'!G9="","",IF('Dati Comparti'!G9&gt;0.12,Parametri!$D$34,IF('Dati Comparti'!G9&gt;=Parametri!$B$35,Parametri!$D$35,IF('Dati Comparti'!G9&gt;=Parametri!$B$36,Parametri!$D$36,IF('Dati Comparti'!G9&gt;=Parametri!$B$37,Parametri!$D$37,IF('Dati Comparti'!G9&gt;=Parametri!$B$38,Parametri!$D$38,Parametri!$D$39))))))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="43">
         <f>IF('Dati Comparti'!J9="","",IF('Dati Comparti'!J9&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J9&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J9&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J9&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J9&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
@@ -2306,7 +2375,7 @@
       </c>
       <c r="G10" s="42">
         <f>IF(OR(C10="",D10="",E10="",F10=""),"",ROUND(C10*Parametri!C6+D10*Parametri!C7+E10*Parametri!C8+F10*Parametri!C9,2))</f>
-        <v>-3.2</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
@@ -2315,7 +2384,7 @@
       </c>
       <c r="C11" s="41">
         <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" s="41">
         <f>IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F10&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F10&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F10&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F10&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2331,29 +2400,29 @@
       </c>
       <c r="G11" s="42">
         <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="59"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="62"/>
       <c r="G14" s="14" t="s">
         <v>12</v>
       </c>
@@ -2362,13 +2431,13 @@
       <c r="B15" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="56" t="str">
+      <c r="C15" s="59" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
       <c r="G15" s="1">
         <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
         <v>7.8</v>
@@ -2378,107 +2447,107 @@
       <c r="B16" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="55" t="str">
+      <c r="C16" s="58" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
-      </c>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
+        <v>Editoria</v>
+      </c>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
       <c r="G16" s="2">
         <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>4.5999999999999996</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="53" t="str">
+      <c r="C17" s="56" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
-        <v>Idrico</v>
-      </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
+        <v>Centro Servizi</v>
+      </c>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
       <c r="G17" s="3">
         <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>2.8</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="52" t="str">
+      <c r="C18" s="55" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
         <v>Medicale</v>
       </c>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
       <c r="G18" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="52" t="str">
+      <c r="C19" s="55" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
-        <v>Gori</v>
-      </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
+        <v>Idrico</v>
+      </c>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>-0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="52" t="str">
+      <c r="C20" s="55" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
       <c r="G20" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
-        <v>-3.2</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="52" t="str">
+      <c r="C21" s="55" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>Igiene Ambientale</v>
       </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
       <c r="G21" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
         <v>-4</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2497,4 +2566,527 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="50" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="52">
+        <v>10</v>
+      </c>
+      <c r="D2" s="52">
+        <v>2</v>
+      </c>
+      <c r="E2" s="52">
+        <v>2</v>
+      </c>
+      <c r="F2" s="52">
+        <v>6</v>
+      </c>
+      <c r="G2" s="52">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="52">
+        <v>-5</v>
+      </c>
+      <c r="D3" s="52">
+        <v>10</v>
+      </c>
+      <c r="E3" s="52">
+        <v>4</v>
+      </c>
+      <c r="F3" s="52">
+        <v>4</v>
+      </c>
+      <c r="G3" s="52">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D4" s="52">
+        <v>10</v>
+      </c>
+      <c r="E4" s="52">
+        <v>2</v>
+      </c>
+      <c r="F4" s="52">
+        <v>4</v>
+      </c>
+      <c r="G4" s="52">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="52">
+        <v>6</v>
+      </c>
+      <c r="D5" s="52">
+        <v>0</v>
+      </c>
+      <c r="E5" s="52">
+        <v>0</v>
+      </c>
+      <c r="F5" s="52">
+        <v>6</v>
+      </c>
+      <c r="G5" s="52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D6" s="52">
+        <v>0</v>
+      </c>
+      <c r="E6" s="52">
+        <v>0</v>
+      </c>
+      <c r="F6" s="52">
+        <v>8</v>
+      </c>
+      <c r="G6" s="52">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D7" s="52">
+        <v>0</v>
+      </c>
+      <c r="E7" s="52">
+        <v>0</v>
+      </c>
+      <c r="F7" s="52">
+        <v>10</v>
+      </c>
+      <c r="G7" s="52">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="69">
+        <v>6</v>
+      </c>
+      <c r="D8" s="69">
+        <v>0</v>
+      </c>
+      <c r="E8" s="69">
+        <v>0</v>
+      </c>
+      <c r="F8" s="69">
+        <v>4</v>
+      </c>
+      <c r="G8" s="69">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="52">
+        <v>10</v>
+      </c>
+      <c r="D9" s="52">
+        <v>0</v>
+      </c>
+      <c r="E9" s="52">
+        <v>0</v>
+      </c>
+      <c r="F9" s="52">
+        <v>6</v>
+      </c>
+      <c r="G9" s="52">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="52">
+        <v>10</v>
+      </c>
+      <c r="D10" s="52">
+        <v>10</v>
+      </c>
+      <c r="E10" s="52">
+        <v>4</v>
+      </c>
+      <c r="F10" s="52">
+        <v>0</v>
+      </c>
+      <c r="G10" s="52">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D11" s="52">
+        <v>10</v>
+      </c>
+      <c r="E11" s="52">
+        <v>2</v>
+      </c>
+      <c r="F11" s="52">
+        <v>4</v>
+      </c>
+      <c r="G11" s="52">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="52">
+        <v>4</v>
+      </c>
+      <c r="D12" s="52">
+        <v>0</v>
+      </c>
+      <c r="E12" s="52">
+        <v>0</v>
+      </c>
+      <c r="F12" s="52">
+        <v>4</v>
+      </c>
+      <c r="G12" s="52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D13" s="52">
+        <v>0</v>
+      </c>
+      <c r="E13" s="52">
+        <v>0</v>
+      </c>
+      <c r="F13" s="52">
+        <v>0</v>
+      </c>
+      <c r="G13" s="52">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D14" s="52">
+        <v>0</v>
+      </c>
+      <c r="E14" s="52">
+        <v>0</v>
+      </c>
+      <c r="F14" s="52">
+        <v>8</v>
+      </c>
+      <c r="G14" s="52">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="69">
+        <v>6</v>
+      </c>
+      <c r="D15" s="69">
+        <v>0</v>
+      </c>
+      <c r="E15" s="69">
+        <v>0</v>
+      </c>
+      <c r="F15" s="69">
+        <v>2</v>
+      </c>
+      <c r="G15" s="69">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="52">
+        <v>10</v>
+      </c>
+      <c r="D16" s="52">
+        <v>0</v>
+      </c>
+      <c r="E16" s="52">
+        <v>0</v>
+      </c>
+      <c r="F16" s="52">
+        <v>6</v>
+      </c>
+      <c r="G16" s="52">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="52">
+        <v>10</v>
+      </c>
+      <c r="D17" s="52">
+        <v>10</v>
+      </c>
+      <c r="E17" s="52">
+        <v>4</v>
+      </c>
+      <c r="F17" s="52">
+        <v>0</v>
+      </c>
+      <c r="G17" s="52">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="52">
+        <v>10</v>
+      </c>
+      <c r="D18" s="52">
+        <v>10</v>
+      </c>
+      <c r="E18" s="52">
+        <v>2</v>
+      </c>
+      <c r="F18" s="52">
+        <v>4</v>
+      </c>
+      <c r="G18" s="52">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="52">
+        <v>6</v>
+      </c>
+      <c r="D19" s="52">
+        <v>0</v>
+      </c>
+      <c r="E19" s="52">
+        <v>0</v>
+      </c>
+      <c r="F19" s="52">
+        <v>6</v>
+      </c>
+      <c r="G19" s="52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D20" s="52">
+        <v>0</v>
+      </c>
+      <c r="E20" s="52">
+        <v>0</v>
+      </c>
+      <c r="F20" s="52">
+        <v>0</v>
+      </c>
+      <c r="G20" s="52">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="52">
+        <v>-10</v>
+      </c>
+      <c r="D21" s="52">
+        <v>2</v>
+      </c>
+      <c r="E21" s="52">
+        <v>2</v>
+      </c>
+      <c r="F21" s="52">
+        <v>8</v>
+      </c>
+      <c r="G21" s="52">
+        <v>-2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="52">
+        <v>10</v>
+      </c>
+      <c r="D22" s="52">
+        <v>0</v>
+      </c>
+      <c r="E22" s="52">
+        <v>0</v>
+      </c>
+      <c r="F22" s="52">
+        <v>2</v>
+      </c>
+      <c r="G22" s="52">
+        <v>4.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB304AE1-355A-4844-9A9B-56A687F65D85}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4AC9A90-7AE8-4249-AF18-AF3AFA757756}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,6 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -805,6 +804,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -845,10 +848,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -989,7 +988,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46244</v>
+            <v>46246</v>
           </cell>
         </row>
       </sheetData>
@@ -1051,19 +1050,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.86899050100283048</v>
+            <v>0.79511434470357545</v>
           </cell>
           <cell r="G4">
-            <v>0.53333333333333333</v>
+            <v>0.49180327868852458</v>
           </cell>
           <cell r="H4">
-            <v>-3.3796156183765171E-2</v>
+            <v>-2.0040620882806129E-2</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>220.71247436136491</v>
+            <v>218.38178004195385</v>
           </cell>
         </row>
         <row r="5">
@@ -1074,7 +1073,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.89382430001142776</v>
+            <v>0.92125900474441191</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1086,7 +1085,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>304.39368474662592</v>
+            <v>303.04878517238069</v>
           </cell>
         </row>
         <row r="6">
@@ -1097,19 +1096,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>1.0921435016397814</v>
+            <v>0.98096439179554551</v>
           </cell>
           <cell r="G6">
-            <v>0.97463768115942029</v>
+            <v>0.9750396895396013</v>
           </cell>
           <cell r="H6">
-            <v>1.4637681159420324E-2</v>
+            <v>1.5039689539601331E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>224.67750929368029</v>
+            <v>224.22614201718679</v>
           </cell>
         </row>
         <row r="7">
@@ -1120,19 +1119,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.65799697583622063</v>
+            <v>0.65472860669475308</v>
           </cell>
           <cell r="G7">
-            <v>0.48214285714285715</v>
+            <v>0.4642857142857143</v>
           </cell>
           <cell r="H7">
-            <v>-5.9696272323367293E-2</v>
+            <v>-5.6842780886532947E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>193.61581454121307</v>
+            <v>195.85740934188928</v>
           </cell>
         </row>
         <row r="8">
@@ -1143,19 +1142,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.46901751304228245</v>
+            <v>0.49760195916154598</v>
           </cell>
           <cell r="G8">
-            <v>0.3125</v>
+            <v>0.375</v>
           </cell>
           <cell r="H8">
-            <v>-5.7467116796869694E-2</v>
+            <v>-5.2552471889165231E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>250.88470588235293</v>
+            <v>262</v>
           </cell>
         </row>
         <row r="9">
@@ -1166,19 +1165,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.47854522084832635</v>
+            <v>0.47859105181726713</v>
           </cell>
           <cell r="G9">
             <v>0.75</v>
           </cell>
           <cell r="H9">
-            <v>1.1361136265038253E-2</v>
+            <v>1.6441079259835345E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>141.72474747474749</v>
+            <v>141.77849860982391</v>
           </cell>
         </row>
         <row r="10">
@@ -1189,19 +1188,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.80676622784243623</v>
+            <v>0.76379830656608505</v>
           </cell>
           <cell r="G10">
-            <v>0.3611111111111111</v>
+            <v>0.41666666666666669</v>
           </cell>
           <cell r="H10">
-            <v>-1.1831147902635845E-2</v>
+            <v>-7.8976422710896957E-3</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>201.43980181668044</v>
+            <v>194.80559748427672</v>
           </cell>
         </row>
       </sheetData>
@@ -1403,19 +1402,19 @@
   <sheetData>
     <row r="1" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="14" t="s">
@@ -1486,11 +1485,11 @@
     </row>
     <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="14" t="s">
@@ -1591,11 +1590,11 @@
     </row>
     <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="14" t="s">
@@ -1674,11 +1673,11 @@
     </row>
     <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="65" t="s">
+      <c r="B32" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="14" t="s">
@@ -1757,11 +1756,11 @@
     </row>
     <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="56"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="14" t="s">
@@ -1882,7 +1881,7 @@
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1-1</f>
-        <v>46243</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1924,19 +1923,19 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.86899050100283048</v>
+        <v>0.79511434470357545</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>0.21906142587768795</v>
+        <v>0.14518526957843292</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.53333333333333333</v>
+        <v>0.49180327868852458</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>-3.3796156183765171E-2</v>
+        <v>-2.0040620882806129E-2</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1944,11 +1943,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>220.71247436136491</v>
+        <v>218.38178004195385</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-4.8948955705324905E-2</v>
+        <v>-5.8991928005922574E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
@@ -1961,11 +1960,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.89382430001142776</v>
+        <v>0.92125900474441191</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>0.13294681220270255</v>
+        <v>0.1603815169356867</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1981,11 +1980,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>304.39368474662592</v>
+        <v>303.04878517238069</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>0.21336151180807594</v>
+        <v>0.20800052877061717</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -1998,19 +1997,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.0921435016397814</v>
+        <v>0.98096439179554551</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>0.30335595491403056</v>
+        <v>0.19217684506979471</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97463768115942029</v>
+        <v>0.9750396895396013</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.4637681159420324E-2</v>
+        <v>1.5039689539601331E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -2018,11 +2017,11 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>224.67750929368029</v>
+        <v>224.22614201718679</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="1"/>
-        <v>2.7330165011084321E-2</v>
+        <v>2.5266303701163197E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
@@ -2035,19 +2034,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65799697583622063</v>
+        <v>0.65472860669475308</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>4.0523053724951463E-2</v>
+        <v>3.725468458348391E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.48214285714285715</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>-5.9696272323367293E-2</v>
+        <v>-5.6842780886532947E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2055,11 +2054,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>193.61581454121307</v>
+        <v>195.85740934188928</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>-3.5575576788798698E-2</v>
+        <v>-2.4409914635435646E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
@@ -2072,19 +2071,19 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.46901751304228245</v>
+        <v>0.49760195916154598</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.16368248695771759</v>
+        <v>-0.13509804083845406</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.3125</v>
+        <v>0.375</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-5.7467116796869694E-2</v>
+        <v>-5.2552471889165231E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2092,11 +2091,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>250.88470588235293</v>
+        <v>262</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.71216834527104866</v>
+        <v>0.78802492118180623</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
@@ -2109,11 +2108,11 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.47854522084832635</v>
+        <v>0.47859105181726713</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.19716031767669356</v>
+        <v>-0.19711448670775278</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2121,7 +2120,7 @@
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.1361136265038253E-2</v>
+        <v>1.6441079259835345E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2129,11 +2128,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>141.72474747474749</v>
+        <v>141.77849860982391</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>-5.3986072484581191E-2</v>
+        <v>-5.3627283188370796E-2</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
@@ -2146,19 +2145,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.80676622784243623</v>
+        <v>0.76379830656608505</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>0.15658257484697924</v>
+        <v>0.11361465357062805</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.3611111111111111</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-1.1831147902635845E-2</v>
+        <v>-7.8976422710896957E-3</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2166,11 +2165,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>201.43980181668044</v>
+        <v>194.80559748427672</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>8.9305316376432284E-2</v>
+        <v>5.3430211337401584E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2194,14 +2193,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
     </row>
     <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="27" t="s">
@@ -2242,11 +2241,11 @@
       </c>
       <c r="F5" s="41">
         <f>IF('Dati Comparti'!J4="","",IF('Dati Comparti'!J4&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J4&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J4&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J4&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J4&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" s="42">
         <f>IF(OR(C5="",D5="",E5="",F5=""),"",ROUND(C5*Parametri!C6+D5*Parametri!C7+E5*Parametri!C8+F5*Parametri!C9,2))</f>
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -2308,7 +2307,7 @@
       </c>
       <c r="C8" s="43">
         <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" s="43">
         <f>IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F7&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F7&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F7&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F7&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2324,7 +2323,7 @@
       </c>
       <c r="G8" s="42">
         <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -2404,25 +2403,25 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="60" t="s">
+      <c r="B13" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="62"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="64"/>
       <c r="G14" s="14" t="s">
         <v>12</v>
       </c>
@@ -2431,13 +2430,13 @@
       <c r="B15" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="59" t="str">
+      <c r="C15" s="61" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
       <c r="G15" s="1">
         <f>IFERROR(LARGE(Scoring!G5:G11,1),"")</f>
         <v>7.8</v>
@@ -2447,13 +2446,13 @@
       <c r="B16" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="58" t="str">
+      <c r="C16" s="60" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
         <v>Editoria</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
       <c r="G16" s="2">
         <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
         <v>7.8</v>
@@ -2463,29 +2462,29 @@
       <c r="B17" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="56" t="str">
+      <c r="C17" s="58" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
         <v>Centro Servizi</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
       <c r="G17" s="3">
         <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="55" t="str">
+      <c r="C18" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
         <v>Medicale</v>
       </c>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
       <c r="G18" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
         <v>4.2</v>
@@ -2495,29 +2494,29 @@
       <c r="B19" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="55" t="str">
+      <c r="C19" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
         <v>Idrico</v>
       </c>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="55" t="str">
+      <c r="C20" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,6),Scoring!G5:G11,0)),"")</f>
         <v>ITS</v>
       </c>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
       <c r="G20" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,6),"")</f>
         <v>-2.2000000000000002</v>
@@ -2527,27 +2526,27 @@
       <c r="B21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="55" t="str">
+      <c r="C21" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,7),Scoring!G5:G11,0)),"")</f>
         <v>Igiene Ambientale</v>
       </c>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
       <c r="G21" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,7),"")</f>
         <v>-4</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2742,25 +2741,25 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="69">
+      <c r="C8" s="54">
         <v>6</v>
       </c>
-      <c r="D8" s="69">
-        <v>0</v>
-      </c>
-      <c r="E8" s="69">
-        <v>0</v>
-      </c>
-      <c r="F8" s="69">
+      <c r="D8" s="54">
+        <v>0</v>
+      </c>
+      <c r="E8" s="54">
+        <v>0</v>
+      </c>
+      <c r="F8" s="54">
         <v>4</v>
       </c>
-      <c r="G8" s="69">
+      <c r="G8" s="54">
         <v>2.8</v>
       </c>
     </row>
@@ -2903,25 +2902,25 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="69">
+      <c r="C15" s="54">
         <v>6</v>
       </c>
-      <c r="D15" s="69">
-        <v>0</v>
-      </c>
-      <c r="E15" s="69">
-        <v>0</v>
-      </c>
-      <c r="F15" s="69">
+      <c r="D15" s="54">
+        <v>0</v>
+      </c>
+      <c r="E15" s="54">
+        <v>0</v>
+      </c>
+      <c r="F15" s="54">
         <v>2</v>
       </c>
-      <c r="G15" s="69">
+      <c r="G15" s="54">
         <v>2.6</v>
       </c>
     </row>
@@ -2942,10 +2941,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="52">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="52">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -3002,7 +3001,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="52">
         <v>0</v>
@@ -3014,7 +3013,7 @@
         <v>6</v>
       </c>
       <c r="G19" s="52">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4AC9A90-7AE8-4249-AF18-AF3AFA757756}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{241D2005-CE7C-4CF2-A9F5-2ABD6ACF240A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -988,7 +988,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46246</v>
+            <v>46250</v>
           </cell>
         </row>
       </sheetData>
@@ -1050,19 +1050,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.79511434470357545</v>
+            <v>0.77637348355085189</v>
           </cell>
           <cell r="G4">
-            <v>0.49180327868852458</v>
+            <v>0.60655737704918034</v>
           </cell>
           <cell r="H4">
-            <v>-2.0040620882806129E-2</v>
+            <v>-7.7073581007164917E-3</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>218.38178004195385</v>
+            <v>219.5099920063949</v>
           </cell>
         </row>
         <row r="5">
@@ -1073,7 +1073,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.92125900474441191</v>
+            <v>0.63495069776162982</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1085,7 +1085,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>303.04878517238069</v>
+            <v>304.10056074766356</v>
           </cell>
         </row>
         <row r="6">
@@ -1096,19 +1096,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.98096439179554551</v>
+            <v>0.93300544619904702</v>
           </cell>
           <cell r="G6">
-            <v>0.9750396895396013</v>
+            <v>0.97367862449586073</v>
           </cell>
           <cell r="H6">
-            <v>1.5039689539601331E-2</v>
+            <v>1.3678624495860769E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>224.22614201718679</v>
+            <v>224.72988881621976</v>
           </cell>
         </row>
         <row r="7">
@@ -1119,19 +1119,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.65472860669475308</v>
+            <v>0.62921617379651473</v>
           </cell>
           <cell r="G7">
-            <v>0.4642857142857143</v>
+            <v>0.5</v>
           </cell>
           <cell r="H7">
-            <v>-5.6842780886532947E-2</v>
+            <v>-4.3832547691899017E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>195.85740934188928</v>
+            <v>196.95480113068555</v>
           </cell>
         </row>
         <row r="8">
@@ -1142,19 +1142,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.49760195916154598</v>
+            <v>0.49371942185240753</v>
           </cell>
           <cell r="G8">
-            <v>0.375</v>
+            <v>0.41176470588235292</v>
           </cell>
           <cell r="H8">
-            <v>-5.2552471889165231E-2</v>
+            <v>-4.2564442913347787E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>262</v>
+            <v>263.32084309133489</v>
           </cell>
         </row>
         <row r="9">
@@ -1165,19 +1165,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.47859105181726713</v>
+            <v>0.45306963459344513</v>
           </cell>
           <cell r="G9">
             <v>0.75</v>
           </cell>
           <cell r="H9">
-            <v>1.6441079259835345E-2</v>
+            <v>1.3321378938177832E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>141.77849860982391</v>
+            <v>139.67159763313609</v>
           </cell>
         </row>
         <row r="10">
@@ -1188,19 +1188,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.76379830656608505</v>
+            <v>0.72618011818023764</v>
           </cell>
           <cell r="G10">
-            <v>0.41666666666666669</v>
+            <v>0.44444444444444442</v>
           </cell>
           <cell r="H10">
-            <v>-7.8976422710896957E-3</v>
+            <v>-4.5710069139451455E-4</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>194.80559748427672</v>
+            <v>194.64928772167846</v>
           </cell>
         </row>
       </sheetData>
@@ -1389,34 +1389,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:D48"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2" style="5" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="5"/>
+    <col min="6" max="6" width="8.7109375" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="55" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="56"/>
       <c r="D2" s="56"/>
     </row>
-    <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="68" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="56"/>
       <c r="D4" s="56"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>23</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
         <v>26</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="17" t="s">
         <v>28</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="18" t="s">
         <v>30</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
         <v>32</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>34</v>
       </c>
@@ -1483,15 +1483,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="69" t="s">
         <v>36</v>
       </c>
       <c r="C12" s="56"/>
       <c r="D12" s="56"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>37</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="21" t="s">
         <v>40</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="23">
         <v>0.06</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="23">
         <v>0.04</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="23">
         <v>0.02</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="23">
         <v>0</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="24">
         <v>-1.9E-2</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="24">
         <v>-3.9E-2</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
         <v>41</v>
       </c>
@@ -1588,15 +1588,15 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="65" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="56"/>
       <c r="D23" s="56"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="14" t="s">
         <v>43</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
         <v>45</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="23">
         <v>0.9</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="23">
         <v>0.85</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="25">
         <v>0.8</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="25">
         <v>0.7</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="26"/>
       <c r="C30" s="24">
         <v>0.69989999999999997</v>
@@ -1671,15 +1671,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="67" t="s">
         <v>47</v>
       </c>
       <c r="C32" s="56"/>
       <c r="D32" s="56"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="14" t="s">
         <v>48</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="21" t="s">
         <v>50</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="23">
         <v>8.1000000000000003E-2</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="23">
         <v>5.0999999999999997E-2</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="25">
         <v>3.1E-2</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="25">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="24" t="s">
         <v>51</v>
       </c>
@@ -1754,15 +1754,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="66" t="s">
         <v>52</v>
       </c>
       <c r="C41" s="56"/>
       <c r="D41" s="56"/>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="14" t="s">
         <v>37</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="21" t="s">
         <v>53</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="23">
         <v>-9.9000000000000005E-2</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="23">
         <v>-4.9000000000000002E-2</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="25">
         <v>0</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="25">
         <v>0.05</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="24">
         <v>0.1</v>
       </c>
@@ -1856,17 +1856,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:J10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="5" customWidth="1"/>
     <col min="2" max="2" width="22" style="5" customWidth="1"/>
     <col min="3" max="10" width="16" style="5" customWidth="1"/>
     <col min="11" max="11" width="2" style="5" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="5"/>
+    <col min="12" max="12" width="8.7109375" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C1" s="47" t="s">
         <v>55</v>
       </c>
@@ -1875,16 +1875,16 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C2" s="47" t="s">
         <v>56</v>
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1-1</f>
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
         <v>65</v>
       </c>
@@ -1923,19 +1923,19 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.79511434470357545</v>
+        <v>0.77637348355085189</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>0.14518526957843292</v>
+        <v>0.12644440842570936</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.49180327868852458</v>
+        <v>0.60655737704918034</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>-2.0040620882806129E-2</v>
+        <v>-7.7073581007164917E-3</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1943,14 +1943,14 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>218.38178004195385</v>
+        <v>219.5099920063949</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-5.8991928005922574E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+        <v>-5.4130457578969532E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="38" t="s">
         <v>66</v>
       </c>
@@ -1960,11 +1960,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.92125900474441191</v>
+        <v>0.63495069776162982</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>0.1603815169356867</v>
+        <v>-0.12592679004709539</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1980,14 +1980,14 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>303.04878517238069</v>
+        <v>304.10056074766356</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>0.20800052877061717</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+        <v>0.21219307305145638</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
         <v>67</v>
       </c>
@@ -1997,19 +1997,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.98096439179554551</v>
+        <v>0.93300544619904702</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>0.19217684506979471</v>
+        <v>0.14421789947329622</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.9750396895396013</v>
+        <v>0.97367862449586073</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.5039689539601331E-2</v>
+        <v>1.3678624495860769E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -2017,14 +2017,14 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>224.22614201718679</v>
+        <v>224.72988881621976</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="1"/>
-        <v>2.5266303701163197E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+        <v>2.7569668572000761E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
         <v>68</v>
       </c>
@@ -2034,19 +2034,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.65472860669475308</v>
+        <v>0.62921617379651473</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>3.725468458348391E-2</v>
+        <v>1.1742251685245564E-2</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.4642857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>-5.6842780886532947E-2</v>
+        <v>-4.3832547691899017E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2054,14 +2054,14 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>195.85740934188928</v>
+        <v>196.95480113068555</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>-2.4409914635435646E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+        <v>-1.8943669817292071E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="32" t="s">
         <v>69</v>
       </c>
@@ -2071,19 +2071,19 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.49760195916154598</v>
+        <v>0.49371942185240753</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.13509804083845406</v>
+        <v>-0.13898057814759252</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.375</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-5.2552471889165231E-2</v>
+        <v>-4.2564442913347787E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2091,14 +2091,14 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>262</v>
+        <v>263.32084309133489</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.78802492118180623</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+        <v>0.79703904470958342</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="38" t="s">
         <v>7</v>
       </c>
@@ -2108,11 +2108,11 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.47859105181726713</v>
+        <v>0.45306963459344513</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.19711448670775278</v>
+        <v>-0.22263590393157479</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.6441079259835345E-2</v>
+        <v>1.3321378938177832E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2128,14 +2128,14 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>141.77849860982391</v>
+        <v>139.67159763313609</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>-5.3627283188370796E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+        <v>-6.7690865613858356E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="32" t="s">
         <v>8</v>
       </c>
@@ -2145,19 +2145,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.76379830656608505</v>
+        <v>0.72618011818023764</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>0.11361465357062805</v>
+        <v>7.5996465184780648E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.41666666666666669</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-7.8976422710896957E-3</v>
+        <v>-4.5710069139451455E-4</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2165,11 +2165,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>194.80559748427672</v>
+        <v>194.64928772167846</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>5.3430211337401584E-2</v>
+        <v>5.25849510965542E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2181,18 +2181,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:G23"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="5" customWidth="1"/>
     <col min="2" max="2" width="22" style="5" customWidth="1"/>
     <col min="3" max="6" width="14" style="5" customWidth="1"/>
     <col min="7" max="7" width="18" style="5" customWidth="1"/>
     <col min="8" max="8" width="2" style="5" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="5"/>
+    <col min="9" max="9" width="8.7109375" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
@@ -2202,7 +2202,7 @@
       <c r="F2" s="56"/>
       <c r="G2" s="56"/>
     </row>
-    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>1</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="str">
         <f>'Dati Comparti'!B4</f>
         <v>Centro Servizi</v>
@@ -2248,14 +2248,14 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="38" t="str">
         <f>'Dati Comparti'!B5</f>
         <v>Editoria</v>
       </c>
       <c r="C6" s="43">
         <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2271,10 +2271,10 @@
       </c>
       <c r="G6" s="42">
         <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="str">
         <f>'Dati Comparti'!B6</f>
         <v>Gori</v>
@@ -2300,14 +2300,14 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="38" t="str">
         <f>'Dati Comparti'!B7</f>
         <v>Idrico</v>
       </c>
       <c r="C8" s="43">
         <f>IF('Dati Comparti'!E7="","",IF('Dati Comparti'!E7&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E7&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E7&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E7&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E7&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E7&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E7&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" s="43">
         <f>IF('Dati Comparti'!F7="","",IF('Dati Comparti'!F7&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F7&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F7&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F7&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F7&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2323,10 +2323,10 @@
       </c>
       <c r="G8" s="42">
         <f>IF(OR(C8="",D8="",E8="",F8=""),"",ROUND(C8*Parametri!C6+D8*Parametri!C7+E8*Parametri!C8+F8*Parametri!C9,2))</f>
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="32" t="str">
         <f>'Dati Comparti'!B8</f>
         <v>Igiene Ambientale</v>
@@ -2352,7 +2352,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="38" t="s">
         <v>7</v>
       </c>
@@ -2377,13 +2377,13 @@
         <v>-2.2000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="32" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="41">
         <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="41">
         <f>IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F10&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F10&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F10&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F10&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2399,10 +2399,10 @@
       </c>
       <c r="G11" s="42">
         <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="62" t="s">
         <v>9</v>
       </c>
@@ -2412,7 +2412,7 @@
       <c r="F13" s="56"/>
       <c r="G13" s="56"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
         <v>10</v>
       </c>
@@ -2426,13 +2426,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="44" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="61" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,1),Scoring!G5:G11,0)),"")</f>
-        <v>Editoria</v>
+        <v>Gori</v>
       </c>
       <c r="D15" s="56"/>
       <c r="E15" s="56"/>
@@ -2442,71 +2442,71 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="45" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="60" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Editoria</v>
+        <v>Centro Servizi</v>
       </c>
       <c r="D16" s="56"/>
       <c r="E16" s="56"/>
       <c r="F16" s="56"/>
       <c r="G16" s="2">
         <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="58" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+        <v>Medicale</v>
       </c>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="56"/>
       <c r="G17" s="3">
         <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Medicale</v>
+        <v>Idrico</v>
       </c>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
       <c r="G18" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
-        <v>Idrico</v>
+        <v>Editoria</v>
       </c>
       <c r="D19" s="56"/>
       <c r="E19" s="56"/>
       <c r="F19" s="56"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
         <v>18</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>-2.2000000000000002</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
         <v>19</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="59" t="s">
         <v>20</v>
       </c>
@@ -2570,7 +2570,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2579,7 +2579,7 @@
     <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>55</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
         <v>71</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
         <v>71</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
         <v>71</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
         <v>71</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="51" t="s">
         <v>71</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>-3.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="51" t="s">
         <v>71</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="53" t="s">
         <v>71</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="51" t="s">
         <v>72</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="51" t="s">
         <v>72</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="51" t="s">
         <v>72</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>72</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>72</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="51" t="s">
         <v>72</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>-3.2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="53" t="s">
         <v>72</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="51" t="s">
         <v>73</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="51" t="s">
         <v>73</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>66</v>
       </c>
       <c r="C17" s="52">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="D17" s="52">
         <v>10</v>
@@ -2967,10 +2967,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="52">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="51" t="s">
         <v>73</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="51" t="s">
         <v>73</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" s="52">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>6</v>
       </c>
       <c r="G19" s="52">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="51" t="s">
         <v>73</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="51" t="s">
         <v>73</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>-2.2000000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="51" t="s">
         <v>73</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="52">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="52">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         <v>2</v>
       </c>
       <c r="G22" s="52">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>

--- a/dati.xlsx
+++ b/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://soluzionimediacom-my.sharepoint.com/personal/silvio_magurno_soluzionimediacom_com/Documents/P&amp;C/Analisi Produttività/Challenge BU Inb/per pagina web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{241D2005-CE7C-4CF2-A9F5-2ABD6ACF240A}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_3986FFDAA71613FBBF4E0ADF7712B152860938D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C41EFA4-E3D0-4528-9A1F-259D3682162B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="810" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -988,7 +988,7 @@
       <sheetData sheetId="15">
         <row r="1">
           <cell r="D1">
-            <v>46250</v>
+            <v>46253</v>
           </cell>
         </row>
       </sheetData>
@@ -1050,19 +1050,19 @@
             <v>0.64992907512514253</v>
           </cell>
           <cell r="E4">
-            <v>0.77637348355085189</v>
+            <v>0.76738889522792042</v>
           </cell>
           <cell r="G4">
-            <v>0.60655737704918034</v>
+            <v>0.59677419354838712</v>
           </cell>
           <cell r="H4">
-            <v>-7.7073581007164917E-3</v>
+            <v>-2.4164115526934572E-3</v>
           </cell>
           <cell r="I4">
             <v>232.07216445995408</v>
           </cell>
           <cell r="J4">
-            <v>219.5099920063949</v>
+            <v>219.4619967329682</v>
           </cell>
         </row>
         <row r="5">
@@ -1073,7 +1073,7 @@
             <v>0.76087748780872522</v>
           </cell>
           <cell r="E5">
-            <v>0.63495069776162982</v>
+            <v>0.82915231930391031</v>
           </cell>
           <cell r="G5">
             <v>1</v>
@@ -1085,7 +1085,7 @@
             <v>250.86808983502152</v>
           </cell>
           <cell r="J5">
-            <v>304.10056074766356</v>
+            <v>302.40592018984574</v>
           </cell>
         </row>
         <row r="6">
@@ -1096,19 +1096,19 @@
             <v>0.7887875467257508</v>
           </cell>
           <cell r="E6">
-            <v>0.93300544619904702</v>
+            <v>0.91681894689734511</v>
           </cell>
           <cell r="G6">
-            <v>0.97367862449586073</v>
+            <v>0.97329993279159288</v>
           </cell>
           <cell r="H6">
-            <v>1.3678624495860769E-2</v>
+            <v>1.3299932791592917E-2</v>
           </cell>
           <cell r="I6">
             <v>218.70039150583702</v>
           </cell>
           <cell r="J6">
-            <v>224.72988881621976</v>
+            <v>224.84846202134338</v>
           </cell>
         </row>
         <row r="7">
@@ -1119,19 +1119,19 @@
             <v>0.61747392211126917</v>
           </cell>
           <cell r="E7">
-            <v>0.62921617379651473</v>
+            <v>0.62458776074800981</v>
           </cell>
           <cell r="G7">
-            <v>0.5</v>
+            <v>0.5892857142857143</v>
           </cell>
           <cell r="H7">
-            <v>-4.3832547691899017E-2</v>
+            <v>-3.2404955073082865E-2</v>
           </cell>
           <cell r="I7">
             <v>200.75789235670646</v>
           </cell>
           <cell r="J7">
-            <v>196.95480113068555</v>
+            <v>197.04982456140351</v>
           </cell>
         </row>
         <row r="8">
@@ -1142,19 +1142,19 @@
             <v>0.63270000000000004</v>
           </cell>
           <cell r="E8">
-            <v>0.49371942185240753</v>
+            <v>0.50473576740689596</v>
           </cell>
           <cell r="G8">
-            <v>0.41176470588235292</v>
+            <v>0.47058823529411764</v>
           </cell>
           <cell r="H8">
-            <v>-4.2564442913347787E-2</v>
+            <v>-3.5093084706142662E-2</v>
           </cell>
           <cell r="I8">
             <v>146.53039613498757</v>
           </cell>
           <cell r="J8">
-            <v>263.32084309133489</v>
+            <v>264.88638497652585</v>
           </cell>
         </row>
         <row r="9">
@@ -1165,19 +1165,19 @@
             <v>0.67570553852501991</v>
           </cell>
           <cell r="E9">
-            <v>0.45306963459344513</v>
+            <v>0.46046782385559709</v>
           </cell>
           <cell r="G9">
             <v>0.75</v>
           </cell>
           <cell r="H9">
-            <v>1.3321378938177832E-2</v>
+            <v>1.5298582461048026E-2</v>
           </cell>
           <cell r="I9">
             <v>149.81253801090318</v>
           </cell>
           <cell r="J9">
-            <v>139.67159763313609</v>
+            <v>137.93966623876764</v>
           </cell>
         </row>
         <row r="10">
@@ -1188,19 +1188,19 @@
             <v>0.650183652995457</v>
           </cell>
           <cell r="E10">
-            <v>0.72618011818023764</v>
+            <v>0.73588770338853715</v>
           </cell>
           <cell r="G10">
-            <v>0.44444444444444442</v>
+            <v>0.47368421052631576</v>
           </cell>
           <cell r="H10">
-            <v>-4.5710069139451455E-4</v>
+            <v>4.0119552990118909E-4</v>
           </cell>
           <cell r="I10">
             <v>184.92501485879896</v>
           </cell>
           <cell r="J10">
-            <v>194.64928772167846</v>
+            <v>191.9507587988376</v>
           </cell>
         </row>
       </sheetData>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D2" s="48">
         <f>'[1]Riepilogo mese per Commessa'!$D$1-1</f>
-        <v>46249</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1923,19 +1923,19 @@
       </c>
       <c r="D4" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.77637348355085189</v>
+        <v>0.76738889522792042</v>
       </c>
       <c r="E4" s="34">
         <f t="shared" ref="E4:E10" si="0">IF(C4=0,"",IF(D4="","",(D4-C4)))</f>
-        <v>0.12644440842570936</v>
+        <v>0.11745982010277789</v>
       </c>
       <c r="F4" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.60655737704918034</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="G4" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>-7.7073581007164917E-3</v>
+        <v>-2.4164115526934572E-3</v>
       </c>
       <c r="H4" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
@@ -1943,11 +1943,11 @@
       </c>
       <c r="I4" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B4,[1]dati_comparti!$B:$B,0))</f>
-        <v>219.5099920063949</v>
+        <v>219.4619967329682</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J10" si="1">IF(H4=0,"",IF(I4="","",(I4-H4)/H4))</f>
-        <v>-5.4130457578969532E-2</v>
+        <v>-5.4337269427940656E-2</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
@@ -1960,11 +1960,11 @@
       </c>
       <c r="D5" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.63495069776162982</v>
+        <v>0.82915231930391031</v>
       </c>
       <c r="E5" s="39">
         <f t="shared" si="0"/>
-        <v>-0.12592679004709539</v>
+        <v>6.8274831495185095E-2</v>
       </c>
       <c r="F5" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
@@ -1980,11 +1980,11 @@
       </c>
       <c r="I5" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B5,[1]dati_comparti!$B:$B,0))</f>
-        <v>304.10056074766356</v>
+        <v>302.40592018984574</v>
       </c>
       <c r="J5" s="39">
         <f t="shared" si="1"/>
-        <v>0.21219307305145638</v>
+        <v>0.20543796697585998</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -1997,19 +1997,19 @@
       </c>
       <c r="D6" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.93300544619904702</v>
+        <v>0.91681894689734511</v>
       </c>
       <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v>0.14421789947329622</v>
+        <v>0.12803140017159431</v>
       </c>
       <c r="F6" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.97367862449586073</v>
+        <v>0.97329993279159288</v>
       </c>
       <c r="G6" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.3678624495860769E-2</v>
+        <v>1.3299932791592917E-2</v>
       </c>
       <c r="H6" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
@@ -2017,11 +2017,11 @@
       </c>
       <c r="I6" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B6,[1]dati_comparti!$B:$B,0))</f>
-        <v>224.72988881621976</v>
+        <v>224.84846202134338</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="1"/>
-        <v>2.7569668572000761E-2</v>
+        <v>2.8111840464365479E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -2034,19 +2034,19 @@
       </c>
       <c r="D7" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.62921617379651473</v>
+        <v>0.62458776074800981</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
-        <v>1.1742251685245564E-2</v>
+        <v>7.1138386367406437E-3</v>
       </c>
       <c r="F7" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.5</v>
+        <v>0.5892857142857143</v>
       </c>
       <c r="G7" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>-4.3832547691899017E-2</v>
+        <v>-3.2404955073082865E-2</v>
       </c>
       <c r="H7" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
@@ -2054,11 +2054,11 @@
       </c>
       <c r="I7" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B7,[1]dati_comparti!$B:$B,0))</f>
-        <v>196.95480113068555</v>
+        <v>197.04982456140351</v>
       </c>
       <c r="J7" s="39">
         <f t="shared" si="1"/>
-        <v>-1.8943669817292071E-2</v>
+        <v>-1.8470346305063116E-2</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="D8" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.49371942185240753</v>
+        <v>0.50473576740689596</v>
       </c>
       <c r="E8" s="34">
         <f t="shared" si="0"/>
-        <v>-0.13898057814759252</v>
+        <v>-0.12796423259310408</v>
       </c>
       <c r="F8" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.41176470588235292</v>
+        <v>0.47058823529411764</v>
       </c>
       <c r="G8" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>-4.2564442913347787E-2</v>
+        <v>-3.5093084706142662E-2</v>
       </c>
       <c r="H8" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
@@ -2091,11 +2091,11 @@
       </c>
       <c r="I8" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B8,[1]dati_comparti!$B:$B,0))</f>
-        <v>263.32084309133489</v>
+        <v>264.88638497652585</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="1"/>
-        <v>0.79703904470958342</v>
+        <v>0.807723120686207</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -2108,11 +2108,11 @@
       </c>
       <c r="D9" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.45306963459344513</v>
+        <v>0.46046782385559709</v>
       </c>
       <c r="E9" s="39">
         <f t="shared" si="0"/>
-        <v>-0.22263590393157479</v>
+        <v>-0.21523771466942282</v>
       </c>
       <c r="F9" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="G9" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>1.3321378938177832E-2</v>
+        <v>1.5298582461048026E-2</v>
       </c>
       <c r="H9" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
@@ -2128,11 +2128,11 @@
       </c>
       <c r="I9" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B9,[1]dati_comparti!$B:$B,0))</f>
-        <v>139.67159763313609</v>
+        <v>137.93966623876764</v>
       </c>
       <c r="J9" s="39">
         <f t="shared" si="1"/>
-        <v>-6.7690865613858356E-2</v>
+        <v>-7.9251522801592519E-2</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -2145,19 +2145,19 @@
       </c>
       <c r="D10" s="33">
         <f>INDEX([1]dati_comparti!E:E,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.72618011818023764</v>
+        <v>0.73588770338853715</v>
       </c>
       <c r="E10" s="34">
         <f t="shared" si="0"/>
-        <v>7.5996465184780648E-2</v>
+        <v>8.5704050393080156E-2</v>
       </c>
       <c r="F10" s="35">
         <f>INDEX([1]dati_comparti!G:G,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>0.44444444444444442</v>
+        <v>0.47368421052631576</v>
       </c>
       <c r="G10" s="36">
         <f>INDEX([1]dati_comparti!H:H,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>-4.5710069139451455E-4</v>
+        <v>4.0119552990118909E-4</v>
       </c>
       <c r="H10" s="37">
         <f>INDEX([1]dati_comparti!I:I,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
@@ -2165,11 +2165,11 @@
       </c>
       <c r="I10" s="37">
         <f>INDEX([1]dati_comparti!J:J,MATCH($B10,[1]dati_comparti!$B:$B,0))</f>
-        <v>194.64928772167846</v>
+        <v>191.9507587988376</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="1"/>
-        <v>5.25849510965542E-2</v>
+        <v>3.7992393540718129E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C6" s="43">
         <f>IF('Dati Comparti'!E5="","",IF('Dati Comparti'!E5&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E5&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E5&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E5&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E5&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E5&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E5&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>-10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="43">
         <f>IF('Dati Comparti'!F5="","",IF('Dati Comparti'!F5&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F5&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F5&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F5&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F5&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G6" s="42">
         <f>IF(OR(C6="",D6="",E6="",F6=""),"",ROUND(C6*Parametri!C6+D6*Parametri!C7+E6*Parametri!C8+F6*Parametri!C9,2))</f>
-        <v>-0.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="C11" s="41">
         <f>IF('Dati Comparti'!E10="","",IF('Dati Comparti'!E10&gt;=0.08,Parametri!$D$14,IF('Dati Comparti'!E10&gt;=Parametri!$B$15,Parametri!$D$15,IF('Dati Comparti'!E10&gt;=Parametri!$B$16,Parametri!$D$16,IF('Dati Comparti'!E10&gt;=Parametri!$B$17,Parametri!$D$17,IF('Dati Comparti'!E10&gt;=Parametri!$B$18,Parametri!$D$18,IF('Dati Comparti'!E10&gt;=Parametri!$B$19,Parametri!$D$19,IF('Dati Comparti'!E10&gt;Parametri!$C$21,Parametri!$D$20,Parametri!$D$21))))))))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" s="41">
         <f>IF('Dati Comparti'!F10="","",IF('Dati Comparti'!F10&gt;=0.95,Parametri!$D$25,IF('Dati Comparti'!F10&gt;=Parametri!$B$26,Parametri!$D$26,IF('Dati Comparti'!F10&gt;=Parametri!$B$27,Parametri!$D$27,IF('Dati Comparti'!F10&gt;=Parametri!$B$28,Parametri!$D$28,IF('Dati Comparti'!F10&gt;=Parametri!$B$29,Parametri!$D$29,Parametri!$D$30))))))</f>
@@ -2395,11 +2395,11 @@
       </c>
       <c r="F11" s="41">
         <f>IF('Dati Comparti'!J10="","",IF('Dati Comparti'!J10&lt;=Parametri!$C$43,Parametri!$D$43,IF('Dati Comparti'!J10&lt;=Parametri!$C$44,Parametri!$D$44,IF('Dati Comparti'!J10&lt;=Parametri!$C$45,Parametri!$D$45,IF('Dati Comparti'!J10&lt;=Parametri!$C$46,Parametri!$D$46,IF('Dati Comparti'!J10&lt;=Parametri!$C$47,Parametri!$D$47,Parametri!$D$48))))))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" s="42">
         <f>IF(OR(C11="",D11="",E11="",F11=""),"",ROUND(C11*Parametri!C6+D11*Parametri!C7+E11*Parametri!C8+F11*Parametri!C9,2))</f>
-        <v>3.4</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -2448,14 +2448,14 @@
       </c>
       <c r="C16" s="60" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,2),Scoring!G5:G11,0)),"")</f>
-        <v>Centro Servizi</v>
+        <v>Editoria</v>
       </c>
       <c r="D16" s="56"/>
       <c r="E16" s="56"/>
       <c r="F16" s="56"/>
       <c r="G16" s="2">
         <f>IFERROR(LARGE(Scoring!G5:G11,2),"")</f>
-        <v>4.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2464,14 +2464,14 @@
       </c>
       <c r="C17" s="58" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,3),Scoring!G5:G11,0)),"")</f>
-        <v>Medicale</v>
+        <v>Centro Servizi</v>
       </c>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
       <c r="F17" s="56"/>
       <c r="G17" s="3">
         <f>IFERROR(LARGE(Scoring!G5:G11,3),"")</f>
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -2480,14 +2480,14 @@
       </c>
       <c r="C18" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,4),Scoring!G5:G11,0)),"")</f>
-        <v>Idrico</v>
+        <v>Medicale</v>
       </c>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
       <c r="G18" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,4),"")</f>
-        <v>1.4</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2496,14 +2496,14 @@
       </c>
       <c r="C19" s="57" t="str">
         <f>IFERROR(INDEX(Scoring!B5:B11,MATCH(LARGE(Scoring!G5:G11,5),Scoring!G5:G11,0)),"")</f>
-        <v>Editoria</v>
+        <v>Idrico</v>
       </c>
       <c r="D19" s="56"/>
       <c r="E19" s="56"/>
       <c r="F19" s="56"/>
       <c r="G19" s="4">
         <f>IFERROR(LARGE(Scoring!G5:G11,5),"")</f>
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2955,7 +2955,7 @@
         <v>66</v>
       </c>
       <c r="C17" s="52">
-        <v>-10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="52">
         <v>10</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="52">
-        <v>-0.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3070,7 +3070,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="52">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D22" s="52">
         <v>0</v>
@@ -3079,10 +3079,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="52">
-        <v>3.4</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
   </sheetData>
